--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 днрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/дв 24,08,26 днрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\24,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D6BD41-7E16-402D-96A2-AFA6F920E2E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F961EF18-1ED4-4ACB-8815-E0C5486DF0D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$139</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1176,9 +1176,10 @@
     <col min="22" max="22" width="10" style="23" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="34" width="6" customWidth="1"/>
-    <col min="35" max="35" width="25.140625" customWidth="1"/>
+    <col min="35" max="35" width="15" customWidth="1"/>
     <col min="36" max="37" width="7" customWidth="1"/>
-    <col min="38" max="51" width="3" customWidth="1"/>
+    <col min="38" max="38" width="8.42578125" customWidth="1"/>
+    <col min="39" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
@@ -1622,7 +1623,10 @@
         <f>SUM(AK6:AK499)</f>
         <v>4029.34</v>
       </c>
-      <c r="AL5" s="16"/>
+      <c r="AL5" s="3">
+        <f>SUM(AL6:AL499)</f>
+        <v>1951.9046000000003</v>
+      </c>
       <c r="AM5" s="16"/>
       <c r="AN5" s="16"/>
       <c r="AO5" s="16"/>
@@ -1734,7 +1738,10 @@
         <f>G6*U6</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="16"/>
+      <c r="AL6" s="16">
+        <f>Q6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AM6" s="16"/>
       <c r="AN6" s="16"/>
       <c r="AO6" s="16"/>
@@ -1858,14 +1865,17 @@
       </c>
       <c r="AI7" s="16"/>
       <c r="AJ7" s="16">
-        <f t="shared" ref="AJ7:AK70" si="9">G7*T7</f>
+        <f t="shared" ref="AJ7:AJ70" si="9">G7*T7</f>
         <v>75.600000000000009</v>
       </c>
       <c r="AK7" s="16">
         <f t="shared" ref="AK7:AK70" si="10">G7*U7</f>
         <v>0</v>
       </c>
-      <c r="AL7" s="16"/>
+      <c r="AL7" s="16">
+        <f t="shared" ref="AL7:AL70" si="11">Q7*G7</f>
+        <v>20.240000000000002</v>
+      </c>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
       <c r="AO7" s="16"/>
@@ -1931,7 +1941,7 @@
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4">
-        <f t="shared" ref="S8:S71" si="11">ROUND(R8,0)</f>
+        <f t="shared" ref="S8:S71" si="12">ROUND(R8,0)</f>
         <v>0</v>
       </c>
       <c r="T8" s="4">
@@ -1941,7 +1951,7 @@
       <c r="U8" s="4"/>
       <c r="V8" s="21"/>
       <c r="W8" s="16">
-        <f t="shared" ref="W8:W71" si="12">(F8+O8+P8+S8)/Q8</f>
+        <f t="shared" ref="W8:W71" si="13">(F8+O8+P8+S8)/Q8</f>
         <v>19.376325308718975</v>
       </c>
       <c r="X8" s="16">
@@ -1989,7 +1999,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL8" s="16"/>
+      <c r="AL8" s="16">
+        <f t="shared" si="11"/>
+        <v>1.6033999999999999</v>
+      </c>
       <c r="AM8" s="16"/>
       <c r="AN8" s="16"/>
       <c r="AO8" s="16"/>
@@ -2060,7 +2073,7 @@
         <v>254</v>
       </c>
       <c r="S9" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>254</v>
       </c>
       <c r="T9" s="4">
@@ -2073,7 +2086,7 @@
       </c>
       <c r="V9" s="21"/>
       <c r="W9" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="X9" s="16">
@@ -2121,7 +2134,10 @@
         <f t="shared" si="10"/>
         <v>31.75</v>
       </c>
-      <c r="AL9" s="16"/>
+      <c r="AL9" s="16">
+        <f t="shared" si="11"/>
+        <v>10.5</v>
+      </c>
       <c r="AM9" s="16"/>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
@@ -2209,7 +2225,7 @@
         <v>100</v>
       </c>
       <c r="W10" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.46580375410614</v>
       </c>
       <c r="X10" s="16">
@@ -2255,7 +2271,10 @@
         <f t="shared" si="10"/>
         <v>398</v>
       </c>
-      <c r="AL10" s="16"/>
+      <c r="AL10" s="16">
+        <f t="shared" si="11"/>
+        <v>215.34819999999999</v>
+      </c>
       <c r="AM10" s="16"/>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
@@ -2321,7 +2340,7 @@
       </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T11" s="4">
@@ -2331,7 +2350,7 @@
       <c r="U11" s="4"/>
       <c r="V11" s="21"/>
       <c r="W11" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>112.99196053352823</v>
       </c>
       <c r="X11" s="16">
@@ -2379,7 +2398,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL11" s="16"/>
+      <c r="AL11" s="16">
+        <f t="shared" si="11"/>
+        <v>1.0946</v>
+      </c>
       <c r="AM11" s="16"/>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
@@ -2450,7 +2472,7 @@
         <v>291.93759999999997</v>
       </c>
       <c r="S12" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>292</v>
       </c>
       <c r="T12" s="4">
@@ -2458,12 +2480,12 @@
         <v>146</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" ref="U12:U13" si="13">ROUND(S12*$U$1,0)</f>
+        <f t="shared" ref="U12:U13" si="14">ROUND(S12*$U$1,0)</f>
         <v>146</v>
       </c>
       <c r="V12" s="21"/>
       <c r="W12" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.0016168567682548</v>
       </c>
       <c r="X12" s="16">
@@ -2509,7 +2531,10 @@
         <f t="shared" si="10"/>
         <v>146</v>
       </c>
-      <c r="AL12" s="16"/>
+      <c r="AL12" s="16">
+        <f t="shared" si="11"/>
+        <v>38.593400000000003</v>
+      </c>
       <c r="AM12" s="16"/>
       <c r="AN12" s="16"/>
       <c r="AO12" s="16"/>
@@ -2590,14 +2615,14 @@
         <v>144</v>
       </c>
       <c r="U13" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>145</v>
       </c>
       <c r="V13" s="21">
         <v>100</v>
       </c>
       <c r="W13" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.078945097616224</v>
       </c>
       <c r="X13" s="16">
@@ -2643,7 +2668,10 @@
         <f t="shared" si="10"/>
         <v>145</v>
       </c>
-      <c r="AL13" s="16"/>
+      <c r="AL13" s="16">
+        <f t="shared" si="11"/>
+        <v>92.710000000000008</v>
+      </c>
       <c r="AM13" s="16"/>
       <c r="AN13" s="16"/>
       <c r="AO13" s="16"/>
@@ -2709,7 +2737,7 @@
       </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T14" s="4">
@@ -2719,7 +2747,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="21"/>
       <c r="W14" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.707317073170735</v>
       </c>
       <c r="X14" s="16">
@@ -2767,7 +2795,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="16"/>
+      <c r="AL14" s="16">
+        <f t="shared" si="11"/>
+        <v>2.0499999999999998</v>
+      </c>
       <c r="AM14" s="16"/>
       <c r="AN14" s="16"/>
       <c r="AO14" s="16"/>
@@ -2838,7 +2869,7 @@
         <v>115.05900000000003</v>
       </c>
       <c r="S15" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>115</v>
       </c>
       <c r="T15" s="4">
@@ -2848,7 +2879,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="21"/>
       <c r="W15" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.996846336405037</v>
       </c>
       <c r="X15" s="16">
@@ -2894,7 +2925,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="16"/>
+      <c r="AL15" s="16">
+        <f t="shared" si="11"/>
+        <v>18.708400000000001</v>
+      </c>
       <c r="AM15" s="16"/>
       <c r="AN15" s="16"/>
       <c r="AO15" s="16"/>
@@ -2974,7 +3008,7 @@
         <v>40</v>
       </c>
       <c r="W16" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18.40909090909091</v>
       </c>
       <c r="X16" s="16">
@@ -3022,7 +3056,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL16" s="16"/>
+      <c r="AL16" s="16">
+        <f t="shared" si="11"/>
+        <v>3.3</v>
+      </c>
       <c r="AM16" s="16"/>
       <c r="AN16" s="16"/>
       <c r="AO16" s="16"/>
@@ -3095,7 +3132,7 @@
         <v>247</v>
       </c>
       <c r="S17" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>247</v>
       </c>
       <c r="T17" s="4">
@@ -3103,12 +3140,12 @@
         <v>123</v>
       </c>
       <c r="U17" s="4">
-        <f t="shared" ref="U17:U18" si="14">ROUND(S17*$U$1,0)</f>
+        <f t="shared" ref="U17:U18" si="15">ROUND(S17*$U$1,0)</f>
         <v>124</v>
       </c>
       <c r="V17" s="21"/>
       <c r="W17" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X17" s="16">
@@ -3154,7 +3191,10 @@
         <f t="shared" si="10"/>
         <v>49.6</v>
       </c>
-      <c r="AL17" s="16"/>
+      <c r="AL17" s="16">
+        <f t="shared" si="11"/>
+        <v>28.960000000000004</v>
+      </c>
       <c r="AM17" s="16"/>
       <c r="AN17" s="16"/>
       <c r="AO17" s="16"/>
@@ -3233,14 +3273,14 @@
         <v>178</v>
       </c>
       <c r="U18" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>178</v>
       </c>
       <c r="V18" s="21">
         <v>40</v>
       </c>
       <c r="W18" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.918595932573657</v>
       </c>
       <c r="X18" s="16">
@@ -3286,7 +3326,10 @@
         <f t="shared" si="10"/>
         <v>178</v>
       </c>
-      <c r="AL18" s="16"/>
+      <c r="AL18" s="16">
+        <f t="shared" si="11"/>
+        <v>43.211600000000004</v>
+      </c>
       <c r="AM18" s="16"/>
       <c r="AN18" s="16"/>
       <c r="AO18" s="16"/>
@@ -3354,7 +3397,7 @@
       </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T19" s="4">
@@ -3364,7 +3407,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="21"/>
       <c r="W19" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>83.13382382183336</v>
       </c>
       <c r="X19" s="16">
@@ -3412,7 +3455,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL19" s="16"/>
+      <c r="AL19" s="16">
+        <f t="shared" si="11"/>
+        <v>1.0058</v>
+      </c>
       <c r="AM19" s="16"/>
       <c r="AN19" s="16"/>
       <c r="AO19" s="16"/>
@@ -3483,7 +3529,7 @@
         <v>163</v>
       </c>
       <c r="S20" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>163</v>
       </c>
       <c r="T20" s="4">
@@ -3493,7 +3539,7 @@
       <c r="U20" s="4"/>
       <c r="V20" s="21"/>
       <c r="W20" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="X20" s="16">
@@ -3539,7 +3585,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL20" s="16"/>
+      <c r="AL20" s="16">
+        <f t="shared" si="11"/>
+        <v>24.96</v>
+      </c>
       <c r="AM20" s="16"/>
       <c r="AN20" s="16"/>
       <c r="AO20" s="16"/>
@@ -3612,7 +3661,7 @@
         <v>430.04600000000005</v>
       </c>
       <c r="S21" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>430</v>
       </c>
       <c r="T21" s="4">
@@ -3620,12 +3669,12 @@
         <v>215</v>
       </c>
       <c r="U21" s="4">
-        <f t="shared" ref="U21:U22" si="15">ROUND(S21*$U$1,0)</f>
+        <f t="shared" ref="U21:U22" si="16">ROUND(S21*$U$1,0)</f>
         <v>215</v>
       </c>
       <c r="V21" s="21"/>
       <c r="W21" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.999283946389378</v>
       </c>
       <c r="X21" s="16">
@@ -3671,7 +3720,10 @@
         <f t="shared" si="10"/>
         <v>215</v>
       </c>
-      <c r="AL21" s="16"/>
+      <c r="AL21" s="16">
+        <f t="shared" si="11"/>
+        <v>64.241</v>
+      </c>
       <c r="AM21" s="16"/>
       <c r="AN21" s="16"/>
       <c r="AO21" s="16"/>
@@ -3751,14 +3803,14 @@
         <v>200</v>
       </c>
       <c r="U22" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>200</v>
       </c>
       <c r="V22" s="21">
         <v>200</v>
       </c>
       <c r="W22" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>28.087557603686637</v>
       </c>
       <c r="X22" s="16">
@@ -3806,7 +3858,10 @@
         <f t="shared" si="10"/>
         <v>44</v>
       </c>
-      <c r="AL22" s="16"/>
+      <c r="AL22" s="16">
+        <f t="shared" si="11"/>
+        <v>9.548</v>
+      </c>
       <c r="AM22" s="16"/>
       <c r="AN22" s="16"/>
       <c r="AO22" s="16"/>
@@ -3875,7 +3930,7 @@
         <v>28.346000000000004</v>
       </c>
       <c r="S23" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="T23" s="4">
@@ -3885,7 +3940,7 @@
       <c r="U23" s="4"/>
       <c r="V23" s="21"/>
       <c r="W23" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11.907089151450053</v>
       </c>
       <c r="X23" s="16">
@@ -3931,7 +3986,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL23" s="16"/>
+      <c r="AL23" s="16">
+        <f t="shared" si="11"/>
+        <v>3.7240000000000002</v>
+      </c>
       <c r="AM23" s="16"/>
       <c r="AN23" s="16"/>
       <c r="AO23" s="16"/>
@@ -3995,7 +4053,7 @@
       </c>
       <c r="R24" s="10"/>
       <c r="S24" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T24" s="4">
@@ -4005,7 +4063,7 @@
       <c r="U24" s="4"/>
       <c r="V24" s="22"/>
       <c r="W24" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X24" s="8" t="e">
@@ -4051,7 +4109,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL24" s="16"/>
+      <c r="AL24" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM24" s="16"/>
       <c r="AN24" s="16"/>
       <c r="AO24" s="16"/>
@@ -4136,7 +4197,7 @@
         <v>40</v>
       </c>
       <c r="W25" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.567120370554896</v>
       </c>
       <c r="X25" s="16">
@@ -4182,7 +4243,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL25" s="16"/>
+      <c r="AL25" s="16">
+        <f t="shared" si="11"/>
+        <v>70.25139999999999</v>
+      </c>
       <c r="AM25" s="16"/>
       <c r="AN25" s="16"/>
       <c r="AO25" s="16"/>
@@ -4253,7 +4317,7 @@
         <v>512</v>
       </c>
       <c r="S26" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>512</v>
       </c>
       <c r="T26" s="4">
@@ -4266,7 +4330,7 @@
       </c>
       <c r="V26" s="21"/>
       <c r="W26" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="X26" s="16">
@@ -4312,7 +4376,10 @@
         <f t="shared" si="10"/>
         <v>23.04</v>
       </c>
-      <c r="AL26" s="16"/>
+      <c r="AL26" s="16">
+        <f t="shared" si="11"/>
+        <v>7.38</v>
+      </c>
       <c r="AM26" s="16"/>
       <c r="AN26" s="16"/>
       <c r="AO26" s="16"/>
@@ -4380,7 +4447,7 @@
         <v>80</v>
       </c>
       <c r="S27" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>80</v>
       </c>
       <c r="T27" s="4">
@@ -4390,7 +4457,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="21"/>
       <c r="W27" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-233.33333333333334</v>
       </c>
       <c r="X27" s="16">
@@ -4436,7 +4503,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL27" s="16"/>
+      <c r="AL27" s="16">
+        <f t="shared" si="11"/>
+        <v>-5.3999999999999999E-2</v>
+      </c>
       <c r="AM27" s="16"/>
       <c r="AN27" s="16"/>
       <c r="AO27" s="16"/>
@@ -4505,7 +4575,7 @@
         <v>23</v>
       </c>
       <c r="S28" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>23</v>
       </c>
       <c r="T28" s="4">
@@ -4515,7 +4585,7 @@
       <c r="U28" s="4"/>
       <c r="V28" s="21"/>
       <c r="W28" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="X28" s="16">
@@ -4563,7 +4633,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL28" s="16"/>
+      <c r="AL28" s="16">
+        <f t="shared" si="11"/>
+        <v>1.08</v>
+      </c>
       <c r="AM28" s="16"/>
       <c r="AN28" s="16"/>
       <c r="AO28" s="16"/>
@@ -4647,7 +4720,7 @@
         <v>50</v>
       </c>
       <c r="W29" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19.526815979207928</v>
       </c>
       <c r="X29" s="16">
@@ -4693,7 +4766,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL29" s="16"/>
+      <c r="AL29" s="16">
+        <f t="shared" si="11"/>
+        <v>51.096400000000003</v>
+      </c>
       <c r="AM29" s="16"/>
       <c r="AN29" s="16"/>
       <c r="AO29" s="16"/>
@@ -4753,7 +4829,7 @@
       </c>
       <c r="R30" s="10"/>
       <c r="S30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T30" s="4">
@@ -4763,7 +4839,7 @@
       <c r="U30" s="4"/>
       <c r="V30" s="22"/>
       <c r="W30" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X30" s="8" t="e">
@@ -4809,7 +4885,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL30" s="16"/>
+      <c r="AL30" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM30" s="16"/>
       <c r="AN30" s="16"/>
       <c r="AO30" s="16"/>
@@ -4880,7 +4959,7 @@
         <v>105</v>
       </c>
       <c r="S31" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>105</v>
       </c>
       <c r="T31" s="4">
@@ -4890,7 +4969,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="21"/>
       <c r="W31" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X31" s="16">
@@ -4936,7 +5015,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL31" s="16"/>
+      <c r="AL31" s="16">
+        <f t="shared" si="11"/>
+        <v>7.4400000000000013</v>
+      </c>
       <c r="AM31" s="16"/>
       <c r="AN31" s="16"/>
       <c r="AO31" s="16"/>
@@ -5009,7 +5091,7 @@
         <v>741.39999999999986</v>
       </c>
       <c r="S32" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>741</v>
       </c>
       <c r="T32" s="4">
@@ -5022,7 +5104,7 @@
       </c>
       <c r="V32" s="21"/>
       <c r="W32" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.996987044290449</v>
       </c>
       <c r="X32" s="16">
@@ -5070,7 +5152,10 @@
         <f t="shared" si="10"/>
         <v>148.4</v>
       </c>
-      <c r="AL32" s="16"/>
+      <c r="AL32" s="16">
+        <f t="shared" si="11"/>
+        <v>53.103999999999999</v>
+      </c>
       <c r="AM32" s="16"/>
       <c r="AN32" s="16"/>
       <c r="AO32" s="16"/>
@@ -5134,7 +5219,7 @@
       </c>
       <c r="R33" s="10"/>
       <c r="S33" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T33" s="4">
@@ -5144,7 +5229,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="22"/>
       <c r="W33" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X33" s="8" t="e">
@@ -5192,7 +5277,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="16"/>
+      <c r="AL33" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM33" s="16"/>
       <c r="AN33" s="16"/>
       <c r="AO33" s="16"/>
@@ -5265,7 +5353,7 @@
         <v>720.68000000000029</v>
       </c>
       <c r="S34" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>721</v>
       </c>
       <c r="T34" s="4">
@@ -5278,7 +5366,7 @@
       </c>
       <c r="V34" s="21"/>
       <c r="W34" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.001719320868256</v>
       </c>
       <c r="X34" s="16">
@@ -5326,7 +5414,10 @@
         <f t="shared" si="10"/>
         <v>144.4</v>
       </c>
-      <c r="AL34" s="16"/>
+      <c r="AL34" s="16">
+        <f t="shared" si="11"/>
+        <v>74.448000000000008</v>
+      </c>
       <c r="AM34" s="16"/>
       <c r="AN34" s="16"/>
       <c r="AO34" s="16"/>
@@ -5392,7 +5483,7 @@
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T35" s="4">
@@ -5402,7 +5493,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="21"/>
       <c r="W35" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29.0625</v>
       </c>
       <c r="X35" s="16">
@@ -5450,7 +5541,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL35" s="16"/>
+      <c r="AL35" s="16">
+        <f t="shared" si="11"/>
+        <v>0.96</v>
+      </c>
       <c r="AM35" s="16"/>
       <c r="AN35" s="16"/>
       <c r="AO35" s="16"/>
@@ -5510,7 +5604,7 @@
       </c>
       <c r="R36" s="10"/>
       <c r="S36" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T36" s="4">
@@ -5520,7 +5614,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="22"/>
       <c r="W36" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X36" s="8" t="e">
@@ -5566,7 +5660,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL36" s="16"/>
+      <c r="AL36" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM36" s="16"/>
       <c r="AN36" s="16"/>
       <c r="AO36" s="16"/>
@@ -5630,7 +5727,7 @@
       </c>
       <c r="R37" s="10"/>
       <c r="S37" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T37" s="4">
@@ -5640,7 +5737,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="22"/>
       <c r="W37" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X37" s="8" t="e">
@@ -5688,7 +5785,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL37" s="16"/>
+      <c r="AL37" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM37" s="16"/>
       <c r="AN37" s="16"/>
       <c r="AO37" s="16"/>
@@ -5736,11 +5836,11 @@
         <v>68</v>
       </c>
       <c r="L38" s="8">
-        <f t="shared" ref="L38:L69" si="16">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="17">E38-K38</f>
         <v>-67</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" ref="M38:M69" si="17">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="18">E38-N38</f>
         <v>1</v>
       </c>
       <c r="N38" s="8"/>
@@ -5749,12 +5849,12 @@
       </c>
       <c r="P38" s="8"/>
       <c r="Q38" s="8">
-        <f t="shared" ref="Q38:Q69" si="18">M38/5</f>
+        <f t="shared" ref="Q38:Q69" si="19">M38/5</f>
         <v>0.2</v>
       </c>
       <c r="R38" s="10"/>
       <c r="S38" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T38" s="4">
@@ -5764,11 +5864,11 @@
       <c r="U38" s="4"/>
       <c r="V38" s="22"/>
       <c r="W38" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X38" s="8">
-        <f t="shared" ref="X38:X69" si="19">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="X38:X69" si="20">(F38+O38+P38)/Q38</f>
         <v>0</v>
       </c>
       <c r="Y38" s="8">
@@ -5812,7 +5912,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL38" s="16"/>
+      <c r="AL38" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM38" s="16"/>
       <c r="AN38" s="16"/>
       <c r="AO38" s="16"/>
@@ -5856,11 +5959,11 @@
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N39" s="8"/>
@@ -5869,12 +5972,12 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R39" s="10"/>
       <c r="S39" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T39" s="4">
@@ -5884,11 +5987,11 @@
       <c r="U39" s="4"/>
       <c r="V39" s="22"/>
       <c r="W39" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X39" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y39" s="8">
@@ -5932,7 +6035,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL39" s="16"/>
+      <c r="AL39" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM39" s="16"/>
       <c r="AN39" s="16"/>
       <c r="AO39" s="16"/>
@@ -5974,23 +6080,23 @@
         <v>15.1</v>
       </c>
       <c r="L40" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-14.1</v>
       </c>
       <c r="M40" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="N40" s="8"/>
       <c r="O40" s="8"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.2</v>
       </c>
       <c r="R40" s="10"/>
       <c r="S40" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T40" s="4">
@@ -6000,11 +6106,11 @@
       <c r="U40" s="4"/>
       <c r="V40" s="22"/>
       <c r="W40" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X40" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Y40" s="8">
@@ -6046,7 +6152,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL40" s="16"/>
+      <c r="AL40" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM40" s="16"/>
       <c r="AN40" s="16"/>
       <c r="AO40" s="16"/>
@@ -6094,11 +6203,11 @@
         <v>78</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-68</v>
       </c>
       <c r="M41" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>-2</v>
       </c>
       <c r="N41" s="8">
@@ -6109,12 +6218,12 @@
       </c>
       <c r="P41" s="8"/>
       <c r="Q41" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-0.4</v>
       </c>
       <c r="R41" s="10"/>
       <c r="S41" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T41" s="4">
@@ -6124,11 +6233,11 @@
       <c r="U41" s="4"/>
       <c r="V41" s="22"/>
       <c r="W41" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-17.5</v>
       </c>
       <c r="X41" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-17.5</v>
       </c>
       <c r="Y41" s="8">
@@ -6172,7 +6281,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL41" s="16"/>
+      <c r="AL41" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM41" s="16"/>
       <c r="AN41" s="16"/>
       <c r="AO41" s="16"/>
@@ -6220,11 +6332,11 @@
         <v>107</v>
       </c>
       <c r="L42" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-82</v>
       </c>
       <c r="M42" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>25</v>
       </c>
       <c r="N42" s="16"/>
@@ -6235,7 +6347,7 @@
         <v>191</v>
       </c>
       <c r="Q42" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="R42" s="4">
@@ -6254,11 +6366,11 @@
         <v>100</v>
       </c>
       <c r="W42" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>101.4</v>
       </c>
       <c r="X42" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>77.8</v>
       </c>
       <c r="Y42" s="16">
@@ -6300,7 +6412,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL42" s="16"/>
+      <c r="AL42" s="16">
+        <f t="shared" si="11"/>
+        <v>1.5</v>
+      </c>
       <c r="AM42" s="16"/>
       <c r="AN42" s="16"/>
       <c r="AO42" s="16"/>
@@ -6348,11 +6463,11 @@
         <v>180.78700000000001</v>
       </c>
       <c r="L43" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4.679000000000002</v>
       </c>
       <c r="M43" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>147.92099999999999</v>
       </c>
       <c r="N43" s="16">
@@ -6365,12 +6480,12 @@
         <v>128</v>
       </c>
       <c r="Q43" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>29.584199999999999</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T43" s="4">
@@ -6380,11 +6495,11 @@
       <c r="U43" s="4"/>
       <c r="V43" s="21"/>
       <c r="W43" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.310943003359901</v>
       </c>
       <c r="X43" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.310943003359901</v>
       </c>
       <c r="Y43" s="16">
@@ -6426,7 +6541,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL43" s="16"/>
+      <c r="AL43" s="16">
+        <f t="shared" si="11"/>
+        <v>29.584199999999999</v>
+      </c>
       <c r="AM43" s="16"/>
       <c r="AN43" s="16"/>
       <c r="AO43" s="16"/>
@@ -6474,11 +6592,11 @@
         <v>71.2</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-7.5090000000000003</v>
       </c>
       <c r="M44" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>63.691000000000003</v>
       </c>
       <c r="N44" s="16"/>
@@ -6487,7 +6605,7 @@
       </c>
       <c r="P44" s="16"/>
       <c r="Q44" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.738200000000001</v>
       </c>
       <c r="R44" s="4">
@@ -6495,7 +6613,7 @@
         <v>84.213999999999999</v>
       </c>
       <c r="S44" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="T44" s="4">
@@ -6505,11 +6623,11 @@
       <c r="U44" s="4"/>
       <c r="V44" s="21"/>
       <c r="W44" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.983200138167089</v>
       </c>
       <c r="X44" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.3888618486128337</v>
       </c>
       <c r="Y44" s="16">
@@ -6551,7 +6669,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL44" s="16"/>
+      <c r="AL44" s="16">
+        <f t="shared" si="11"/>
+        <v>12.738200000000001</v>
+      </c>
       <c r="AM44" s="16"/>
       <c r="AN44" s="16"/>
       <c r="AO44" s="16"/>
@@ -6599,11 +6720,11 @@
         <v>177.697</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-10.055000000000007</v>
       </c>
       <c r="M45" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>135.94499999999999</v>
       </c>
       <c r="N45" s="16">
@@ -6614,7 +6735,7 @@
       </c>
       <c r="P45" s="16"/>
       <c r="Q45" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>27.189</v>
       </c>
       <c r="R45" s="4">
@@ -6622,7 +6743,7 @@
         <v>209.18899999999999</v>
       </c>
       <c r="S45" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>209</v>
       </c>
       <c r="T45" s="4">
@@ -6635,11 +6756,11 @@
       </c>
       <c r="V45" s="21"/>
       <c r="W45" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.993048659384311</v>
       </c>
       <c r="X45" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.3061164441502076</v>
       </c>
       <c r="Y45" s="16">
@@ -6681,7 +6802,10 @@
         <f t="shared" si="10"/>
         <v>105</v>
       </c>
-      <c r="AL45" s="16"/>
+      <c r="AL45" s="16">
+        <f t="shared" si="11"/>
+        <v>27.189</v>
+      </c>
       <c r="AM45" s="16"/>
       <c r="AN45" s="16"/>
       <c r="AO45" s="16"/>
@@ -6729,11 +6853,11 @@
         <v>197.48</v>
       </c>
       <c r="L46" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-15.206999999999994</v>
       </c>
       <c r="M46" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>151.09299999999999</v>
       </c>
       <c r="N46" s="16">
@@ -6746,7 +6870,7 @@
         <v>125</v>
       </c>
       <c r="Q46" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>30.218599999999999</v>
       </c>
       <c r="R46" s="4">
@@ -6754,7 +6878,7 @@
         <v>55.037000000000006</v>
       </c>
       <c r="S46" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>55</v>
       </c>
       <c r="T46" s="4">
@@ -6764,11 +6888,11 @@
       <c r="U46" s="4"/>
       <c r="V46" s="21"/>
       <c r="W46" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.998775588544802</v>
       </c>
       <c r="X46" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>13.178704506495999</v>
       </c>
       <c r="Y46" s="16">
@@ -6810,7 +6934,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL46" s="16"/>
+      <c r="AL46" s="16">
+        <f t="shared" si="11"/>
+        <v>30.218599999999999</v>
+      </c>
       <c r="AM46" s="16"/>
       <c r="AN46" s="16"/>
       <c r="AO46" s="16"/>
@@ -6852,11 +6979,11 @@
         <v>85</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-25</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N47" s="8">
@@ -6865,12 +6992,12 @@
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
       <c r="Q47" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R47" s="10"/>
       <c r="S47" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T47" s="4">
@@ -6880,11 +7007,11 @@
       <c r="U47" s="4"/>
       <c r="V47" s="22"/>
       <c r="W47" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X47" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y47" s="8">
@@ -6926,7 +7053,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL47" s="16"/>
+      <c r="AL47" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM47" s="16"/>
       <c r="AN47" s="16"/>
       <c r="AO47" s="16"/>
@@ -6974,11 +7104,11 @@
         <v>342</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-131</v>
       </c>
       <c r="M48" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>179</v>
       </c>
       <c r="N48" s="16">
@@ -6989,7 +7119,7 @@
       </c>
       <c r="P48" s="16"/>
       <c r="Q48" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>35.799999999999997</v>
       </c>
       <c r="R48" s="4">
@@ -6997,7 +7127,7 @@
         <v>273.19999999999993</v>
       </c>
       <c r="S48" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>273</v>
       </c>
       <c r="T48" s="4">
@@ -7010,11 +7140,11 @@
       </c>
       <c r="V48" s="21"/>
       <c r="W48" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13.994413407821231</v>
       </c>
       <c r="X48" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.3687150837988833</v>
       </c>
       <c r="Y48" s="16">
@@ -7058,7 +7188,10 @@
         <f t="shared" si="10"/>
         <v>41.1</v>
       </c>
-      <c r="AL48" s="16"/>
+      <c r="AL48" s="16">
+        <f t="shared" si="11"/>
+        <v>10.739999999999998</v>
+      </c>
       <c r="AM48" s="16"/>
       <c r="AN48" s="16"/>
       <c r="AO48" s="16"/>
@@ -7094,11 +7227,11 @@
       <c r="J49" s="16"/>
       <c r="K49" s="16"/>
       <c r="L49" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M49" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N49" s="16"/>
@@ -7107,12 +7240,12 @@
       </c>
       <c r="P49" s="16"/>
       <c r="Q49" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T49" s="4">
@@ -7122,11 +7255,11 @@
       <c r="U49" s="4"/>
       <c r="V49" s="21"/>
       <c r="W49" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X49" s="16" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y49" s="16">
@@ -7170,7 +7303,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL49" s="16"/>
+      <c r="AL49" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM49" s="16"/>
       <c r="AN49" s="16"/>
       <c r="AO49" s="16"/>
@@ -7212,11 +7348,11 @@
         <v>15</v>
       </c>
       <c r="L50" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-15</v>
       </c>
       <c r="M50" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N50" s="16"/>
@@ -7225,14 +7361,14 @@
       </c>
       <c r="P50" s="16"/>
       <c r="Q50" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R50" s="4">
         <v>15</v>
       </c>
       <c r="S50" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="T50" s="4">
@@ -7242,11 +7378,11 @@
       <c r="U50" s="4"/>
       <c r="V50" s="21"/>
       <c r="W50" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X50" s="16" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y50" s="16">
@@ -7290,7 +7426,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL50" s="16"/>
+      <c r="AL50" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM50" s="16"/>
       <c r="AN50" s="16"/>
       <c r="AO50" s="16"/>
@@ -7338,11 +7477,11 @@
         <v>1148</v>
       </c>
       <c r="L51" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-125</v>
       </c>
       <c r="M51" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>967</v>
       </c>
       <c r="N51" s="16">
@@ -7355,7 +7494,7 @@
         <v>850</v>
       </c>
       <c r="Q51" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>193.4</v>
       </c>
       <c r="R51" s="4">
@@ -7363,7 +7502,7 @@
         <v>763</v>
       </c>
       <c r="S51" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>763</v>
       </c>
       <c r="T51" s="4">
@@ -7376,11 +7515,11 @@
       </c>
       <c r="V51" s="21"/>
       <c r="W51" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="X51" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.054808686659772</v>
       </c>
       <c r="Y51" s="16">
@@ -7424,7 +7563,10 @@
         <f t="shared" si="10"/>
         <v>133.69999999999999</v>
       </c>
-      <c r="AL51" s="16"/>
+      <c r="AL51" s="16">
+        <f t="shared" si="11"/>
+        <v>67.69</v>
+      </c>
       <c r="AM51" s="16"/>
       <c r="AN51" s="16"/>
       <c r="AO51" s="16"/>
@@ -7468,11 +7610,11 @@
         <v>1</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N52" s="8"/>
@@ -7481,12 +7623,12 @@
       </c>
       <c r="P52" s="8"/>
       <c r="Q52" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R52" s="10"/>
       <c r="S52" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T52" s="4">
@@ -7496,11 +7638,11 @@
       <c r="U52" s="4"/>
       <c r="V52" s="22"/>
       <c r="W52" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X52" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y52" s="8">
@@ -7542,7 +7684,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL52" s="16"/>
+      <c r="AL52" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM52" s="16"/>
       <c r="AN52" s="16"/>
       <c r="AO52" s="16"/>
@@ -7590,11 +7735,11 @@
         <v>413</v>
       </c>
       <c r="L53" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-142.10000000000002</v>
       </c>
       <c r="M53" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>222.89999999999998</v>
       </c>
       <c r="N53" s="16">
@@ -7605,7 +7750,7 @@
       </c>
       <c r="P53" s="16"/>
       <c r="Q53" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>44.58</v>
       </c>
       <c r="R53" s="4">
@@ -7613,7 +7758,7 @@
         <v>270.69999999999993</v>
       </c>
       <c r="S53" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>271</v>
       </c>
       <c r="T53" s="4">
@@ -7626,11 +7771,11 @@
       </c>
       <c r="V53" s="21"/>
       <c r="W53" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.006729475100943</v>
       </c>
       <c r="X53" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.9277703005832212</v>
       </c>
       <c r="Y53" s="16">
@@ -7672,7 +7817,10 @@
         <f t="shared" si="10"/>
         <v>55.76</v>
       </c>
-      <c r="AL53" s="16"/>
+      <c r="AL53" s="16">
+        <f t="shared" si="11"/>
+        <v>18.277799999999999</v>
+      </c>
       <c r="AM53" s="16"/>
       <c r="AN53" s="16"/>
       <c r="AO53" s="16"/>
@@ -7720,11 +7868,11 @@
         <v>159</v>
       </c>
       <c r="L54" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-9</v>
       </c>
       <c r="M54" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>150</v>
       </c>
       <c r="N54" s="16"/>
@@ -7733,7 +7881,7 @@
       </c>
       <c r="P54" s="16"/>
       <c r="Q54" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>30</v>
       </c>
       <c r="R54" s="4">
@@ -7741,7 +7889,7 @@
         <v>196</v>
       </c>
       <c r="S54" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>196</v>
       </c>
       <c r="T54" s="4">
@@ -7751,11 +7899,11 @@
       <c r="U54" s="4"/>
       <c r="V54" s="21"/>
       <c r="W54" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="X54" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.4666666666666666</v>
       </c>
       <c r="Y54" s="16">
@@ -7797,7 +7945,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL54" s="16"/>
+      <c r="AL54" s="16">
+        <f t="shared" si="11"/>
+        <v>12.299999999999999</v>
+      </c>
       <c r="AM54" s="16"/>
       <c r="AN54" s="16"/>
       <c r="AO54" s="16"/>
@@ -7839,11 +7990,11 @@
         <v>16</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M55" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N55" s="8">
@@ -7852,12 +8003,12 @@
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R55" s="10"/>
       <c r="S55" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T55" s="4">
@@ -7867,11 +8018,11 @@
       <c r="U55" s="4"/>
       <c r="V55" s="22"/>
       <c r="W55" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X55" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y55" s="8">
@@ -7913,7 +8064,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL55" s="16"/>
+      <c r="AL55" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM55" s="16"/>
       <c r="AN55" s="16"/>
       <c r="AO55" s="16"/>
@@ -7951,23 +8105,23 @@
       <c r="J56" s="8"/>
       <c r="K56" s="8"/>
       <c r="L56" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M56" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R56" s="10"/>
       <c r="S56" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T56" s="4">
@@ -7977,11 +8131,11 @@
       <c r="U56" s="4"/>
       <c r="V56" s="22"/>
       <c r="W56" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X56" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y56" s="8">
@@ -8023,7 +8177,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL56" s="16"/>
+      <c r="AL56" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM56" s="16"/>
       <c r="AN56" s="16"/>
       <c r="AO56" s="16"/>
@@ -8069,11 +8226,11 @@
         <v>382</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-155</v>
       </c>
       <c r="M57" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>131</v>
       </c>
       <c r="N57" s="16">
@@ -8086,7 +8243,7 @@
         <v>255</v>
       </c>
       <c r="Q57" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>26.2</v>
       </c>
       <c r="R57" s="4"/>
@@ -8103,11 +8260,11 @@
         <v>50</v>
       </c>
       <c r="W57" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.335877862595421</v>
       </c>
       <c r="X57" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>19.427480916030536</v>
       </c>
       <c r="Y57" s="16">
@@ -8149,7 +8306,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL57" s="16"/>
+      <c r="AL57" s="16">
+        <f t="shared" si="11"/>
+        <v>9.4319999999999986</v>
+      </c>
       <c r="AM57" s="16"/>
       <c r="AN57" s="16"/>
       <c r="AO57" s="16"/>
@@ -8191,11 +8351,11 @@
         <v>8.7170000000000005</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M58" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N58" s="8">
@@ -8204,12 +8364,12 @@
       <c r="O58" s="8"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R58" s="10"/>
       <c r="S58" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T58" s="4">
@@ -8219,11 +8379,11 @@
       <c r="U58" s="4"/>
       <c r="V58" s="22"/>
       <c r="W58" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X58" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y58" s="8">
@@ -8265,7 +8425,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL58" s="16"/>
+      <c r="AL58" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM58" s="16"/>
       <c r="AN58" s="16"/>
       <c r="AO58" s="16"/>
@@ -8313,11 +8476,11 @@
         <v>362</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-58</v>
       </c>
       <c r="M59" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>304</v>
       </c>
       <c r="N59" s="16"/>
@@ -8326,7 +8489,7 @@
       </c>
       <c r="P59" s="16"/>
       <c r="Q59" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>60.8</v>
       </c>
       <c r="R59" s="4">
@@ -8334,7 +8497,7 @@
         <v>283.19999999999993</v>
       </c>
       <c r="S59" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>283</v>
       </c>
       <c r="T59" s="4">
@@ -8347,11 +8510,11 @@
       </c>
       <c r="V59" s="21"/>
       <c r="W59" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13.996710526315789</v>
       </c>
       <c r="X59" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.3421052631578956</v>
       </c>
       <c r="Y59" s="16">
@@ -8393,7 +8556,10 @@
         <f t="shared" si="10"/>
         <v>46.86</v>
       </c>
-      <c r="AL59" s="16"/>
+      <c r="AL59" s="16">
+        <f t="shared" si="11"/>
+        <v>20.064</v>
+      </c>
       <c r="AM59" s="16"/>
       <c r="AN59" s="16"/>
       <c r="AO59" s="16"/>
@@ -8441,11 +8607,11 @@
         <v>94</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M60" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>90</v>
       </c>
       <c r="N60" s="16"/>
@@ -8454,12 +8620,12 @@
       </c>
       <c r="P60" s="16"/>
       <c r="Q60" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18</v>
       </c>
       <c r="R60" s="4"/>
       <c r="S60" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T60" s="4">
@@ -8469,11 +8635,11 @@
       <c r="U60" s="4"/>
       <c r="V60" s="21"/>
       <c r="W60" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19.277777777777779</v>
       </c>
       <c r="X60" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>19.277777777777779</v>
       </c>
       <c r="Y60" s="16">
@@ -8515,7 +8681,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL60" s="16"/>
+      <c r="AL60" s="16">
+        <f t="shared" si="11"/>
+        <v>7.2</v>
+      </c>
       <c r="AM60" s="16"/>
       <c r="AN60" s="16"/>
       <c r="AO60" s="16"/>
@@ -8563,11 +8732,11 @@
         <v>9</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-3</v>
       </c>
       <c r="M61" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6</v>
       </c>
       <c r="N61" s="16"/>
@@ -8576,12 +8745,12 @@
       </c>
       <c r="P61" s="16"/>
       <c r="Q61" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1.2</v>
       </c>
       <c r="R61" s="4"/>
       <c r="S61" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T61" s="4">
@@ -8591,11 +8760,11 @@
       <c r="U61" s="4"/>
       <c r="V61" s="21"/>
       <c r="W61" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39.166666666666671</v>
       </c>
       <c r="X61" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>39.166666666666671</v>
       </c>
       <c r="Y61" s="16">
@@ -8637,7 +8806,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL61" s="16"/>
+      <c r="AL61" s="16">
+        <f t="shared" si="11"/>
+        <v>0.39600000000000002</v>
+      </c>
       <c r="AM61" s="16"/>
       <c r="AN61" s="16"/>
       <c r="AO61" s="16"/>
@@ -8685,11 +8857,11 @@
         <v>413.49599999999998</v>
       </c>
       <c r="L62" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-19.225999999999999</v>
       </c>
       <c r="M62" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>361.07399999999996</v>
       </c>
       <c r="N62" s="16">
@@ -8702,14 +8874,14 @@
         <v>521</v>
       </c>
       <c r="Q62" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>72.214799999999997</v>
       </c>
       <c r="R62" s="4">
         <v>100</v>
       </c>
       <c r="S62" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="T62" s="4">
@@ -8719,11 +8891,11 @@
       <c r="U62" s="4"/>
       <c r="V62" s="21"/>
       <c r="W62" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.752521643762776</v>
       </c>
       <c r="X62" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15.367763948664264</v>
       </c>
       <c r="Y62" s="16">
@@ -8765,7 +8937,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL62" s="16"/>
+      <c r="AL62" s="16">
+        <f t="shared" si="11"/>
+        <v>72.214799999999997</v>
+      </c>
       <c r="AM62" s="16"/>
       <c r="AN62" s="16"/>
       <c r="AO62" s="16"/>
@@ -8813,11 +8988,11 @@
         <v>43</v>
       </c>
       <c r="L63" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-41</v>
       </c>
       <c r="M63" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="N63" s="16"/>
@@ -8826,12 +9001,12 @@
       </c>
       <c r="P63" s="16"/>
       <c r="Q63" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.4</v>
       </c>
       <c r="R63" s="4"/>
       <c r="S63" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T63" s="4">
@@ -8841,11 +9016,11 @@
       <c r="U63" s="4"/>
       <c r="V63" s="21"/>
       <c r="W63" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>182.5</v>
       </c>
       <c r="X63" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>182.5</v>
       </c>
       <c r="Y63" s="16">
@@ -8887,7 +9062,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL63" s="16"/>
+      <c r="AL63" s="16">
+        <f t="shared" si="11"/>
+        <v>0.16000000000000003</v>
+      </c>
       <c r="AM63" s="16"/>
       <c r="AN63" s="16"/>
       <c r="AO63" s="16"/>
@@ -8935,11 +9113,11 @@
         <v>51.6</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-39.779000000000003</v>
       </c>
       <c r="M64" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>11.821</v>
       </c>
       <c r="N64" s="16"/>
@@ -8948,14 +9126,14 @@
       </c>
       <c r="P64" s="16"/>
       <c r="Q64" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.3641999999999999</v>
       </c>
       <c r="R64" s="4">
         <v>15</v>
       </c>
       <c r="S64" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="T64" s="4">
@@ -8965,11 +9143,11 @@
       <c r="U64" s="4"/>
       <c r="V64" s="21"/>
       <c r="W64" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23.671855172997212</v>
       </c>
       <c r="X64" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>17.327214279671772</v>
       </c>
       <c r="Y64" s="16">
@@ -9011,7 +9189,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL64" s="16"/>
+      <c r="AL64" s="16">
+        <f t="shared" si="11"/>
+        <v>2.3641999999999999</v>
+      </c>
       <c r="AM64" s="16"/>
       <c r="AN64" s="16"/>
       <c r="AO64" s="16"/>
@@ -9059,11 +9240,11 @@
         <v>34.1</v>
       </c>
       <c r="L65" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8.4150000000000027</v>
       </c>
       <c r="M65" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>25.684999999999999</v>
       </c>
       <c r="N65" s="16"/>
@@ -9072,7 +9253,7 @@
       </c>
       <c r="P65" s="16"/>
       <c r="Q65" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5.1369999999999996</v>
       </c>
       <c r="R65" s="4">
@@ -9080,7 +9261,7 @@
         <v>43.573999999999991</v>
       </c>
       <c r="S65" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>44</v>
       </c>
       <c r="T65" s="4">
@@ -9090,11 +9271,11 @@
       <c r="U65" s="4"/>
       <c r="V65" s="21"/>
       <c r="W65" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.082927778859258</v>
       </c>
       <c r="X65" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.5176172863539032</v>
       </c>
       <c r="Y65" s="16">
@@ -9136,7 +9317,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL65" s="16"/>
+      <c r="AL65" s="16">
+        <f t="shared" si="11"/>
+        <v>5.1369999999999996</v>
+      </c>
       <c r="AM65" s="16"/>
       <c r="AN65" s="16"/>
       <c r="AO65" s="16"/>
@@ -9184,11 +9368,11 @@
         <v>6</v>
       </c>
       <c r="L66" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M66" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2</v>
       </c>
       <c r="N66" s="16"/>
@@ -9197,12 +9381,12 @@
       </c>
       <c r="P66" s="16"/>
       <c r="Q66" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.4</v>
       </c>
       <c r="R66" s="4"/>
       <c r="S66" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T66" s="4">
@@ -9212,11 +9396,11 @@
       <c r="U66" s="4"/>
       <c r="V66" s="21"/>
       <c r="W66" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="X66" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>70</v>
       </c>
       <c r="Y66" s="16">
@@ -9258,7 +9442,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL66" s="16"/>
+      <c r="AL66" s="16">
+        <f t="shared" si="11"/>
+        <v>0.24</v>
+      </c>
       <c r="AM66" s="16"/>
       <c r="AN66" s="16"/>
       <c r="AO66" s="16"/>
@@ -9294,11 +9481,11 @@
       <c r="J67" s="12"/>
       <c r="K67" s="12"/>
       <c r="L67" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M67" s="12">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N67" s="12"/>
@@ -9307,12 +9494,12 @@
       </c>
       <c r="P67" s="12"/>
       <c r="Q67" s="12">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R67" s="14"/>
       <c r="S67" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T67" s="4">
@@ -9322,11 +9509,11 @@
       <c r="U67" s="4"/>
       <c r="V67" s="20"/>
       <c r="W67" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X67" s="12" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y67" s="12">
@@ -9370,7 +9557,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL67" s="16"/>
+      <c r="AL67" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM67" s="16"/>
       <c r="AN67" s="16"/>
       <c r="AO67" s="16"/>
@@ -9412,11 +9602,11 @@
         <v>40</v>
       </c>
       <c r="L68" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M68" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N68" s="8">
@@ -9425,12 +9615,12 @@
       <c r="O68" s="8"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R68" s="10"/>
       <c r="S68" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T68" s="4">
@@ -9440,11 +9630,11 @@
       <c r="U68" s="4"/>
       <c r="V68" s="22"/>
       <c r="W68" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X68" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y68" s="8">
@@ -9486,7 +9676,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL68" s="16"/>
+      <c r="AL68" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM68" s="16"/>
       <c r="AN68" s="16"/>
       <c r="AO68" s="16"/>
@@ -9528,11 +9721,11 @@
         <v>8.6</v>
       </c>
       <c r="L69" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-8.6</v>
       </c>
       <c r="M69" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N69" s="8"/>
@@ -9541,12 +9734,12 @@
       </c>
       <c r="P69" s="8"/>
       <c r="Q69" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="R69" s="10"/>
       <c r="S69" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T69" s="4">
@@ -9556,11 +9749,11 @@
       <c r="U69" s="4"/>
       <c r="V69" s="22"/>
       <c r="W69" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X69" s="8" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y69" s="8">
@@ -9602,7 +9795,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL69" s="16"/>
+      <c r="AL69" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM69" s="16"/>
       <c r="AN69" s="16"/>
       <c r="AO69" s="16"/>
@@ -9646,11 +9842,11 @@
       </c>
       <c r="K70" s="8"/>
       <c r="L70" s="8">
-        <f t="shared" ref="L70:L101" si="20">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
         <v>0</v>
       </c>
       <c r="M70" s="8">
-        <f t="shared" ref="M70:M101" si="21">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="22">E70-N70</f>
         <v>0</v>
       </c>
       <c r="N70" s="8"/>
@@ -9659,12 +9855,12 @@
       </c>
       <c r="P70" s="8"/>
       <c r="Q70" s="8">
-        <f t="shared" ref="Q70:Q101" si="22">M70/5</f>
+        <f t="shared" ref="Q70:Q101" si="23">M70/5</f>
         <v>0</v>
       </c>
       <c r="R70" s="10"/>
       <c r="S70" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T70" s="4">
@@ -9674,11 +9870,11 @@
       <c r="U70" s="4"/>
       <c r="V70" s="22"/>
       <c r="W70" s="16" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X70" s="8" t="e">
-        <f t="shared" ref="X70:X101" si="23">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="X70:X101" si="24">(F70+O70+P70)/Q70</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y70" s="8">
@@ -9720,7 +9916,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL70" s="16"/>
+      <c r="AL70" s="16">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM70" s="16"/>
       <c r="AN70" s="16"/>
       <c r="AO70" s="16"/>
@@ -9768,11 +9967,11 @@
         <v>85</v>
       </c>
       <c r="L71" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-6</v>
       </c>
       <c r="M71" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>63</v>
       </c>
       <c r="N71" s="16">
@@ -9783,28 +9982,28 @@
       </c>
       <c r="P71" s="16"/>
       <c r="Q71" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.6</v>
       </c>
       <c r="R71" s="4">
         <v>8</v>
       </c>
       <c r="S71" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="T71" s="4">
-        <f t="shared" ref="T71:T134" si="24">ROUND(S71-U71,0)</f>
+        <f t="shared" ref="T71:T134" si="25">ROUND(S71-U71,0)</f>
         <v>8</v>
       </c>
       <c r="U71" s="4"/>
       <c r="V71" s="21"/>
       <c r="W71" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.15873015873016</v>
       </c>
       <c r="X71" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.523809523809524</v>
       </c>
       <c r="Y71" s="16">
@@ -9841,14 +10040,17 @@
         <v>41</v>
       </c>
       <c r="AJ71" s="16">
-        <f t="shared" ref="AJ71:AK134" si="25">G71*T71</f>
+        <f t="shared" ref="AJ71:AJ134" si="26">G71*T71</f>
         <v>2</v>
       </c>
       <c r="AK71" s="16">
-        <f t="shared" ref="AK71:AK134" si="26">G71*U71</f>
-        <v>0</v>
-      </c>
-      <c r="AL71" s="16"/>
+        <f t="shared" ref="AK71:AK134" si="27">G71*U71</f>
+        <v>0</v>
+      </c>
+      <c r="AL71" s="16">
+        <f t="shared" ref="AL71:AL134" si="28">Q71*G71</f>
+        <v>3.15</v>
+      </c>
       <c r="AM71" s="16"/>
       <c r="AN71" s="16"/>
       <c r="AO71" s="16"/>
@@ -9896,11 +10098,11 @@
         <v>24.2</v>
       </c>
       <c r="L72" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-10.285</v>
       </c>
       <c r="M72" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>13.914999999999999</v>
       </c>
       <c r="N72" s="16"/>
@@ -9909,28 +10111,28 @@
       </c>
       <c r="P72" s="16"/>
       <c r="Q72" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.7829999999999999</v>
       </c>
       <c r="R72" s="4">
         <v>6</v>
       </c>
       <c r="S72" s="4">
-        <f t="shared" ref="S72:S133" si="27">ROUND(R72,0)</f>
+        <f t="shared" ref="S72:S133" si="29">ROUND(R72,0)</f>
         <v>6</v>
       </c>
       <c r="T72" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6</v>
       </c>
       <c r="U72" s="4"/>
       <c r="V72" s="21"/>
       <c r="W72" s="16">
-        <f t="shared" ref="W72:W135" si="28">(F72+O72+P72+S72)/Q72</f>
+        <f t="shared" ref="W72:W135" si="30">(F72+O72+P72+S72)/Q72</f>
         <v>18.299317283507008</v>
       </c>
       <c r="X72" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>16.143370463528566</v>
       </c>
       <c r="Y72" s="16">
@@ -9965,14 +10167,17 @@
       </c>
       <c r="AI72" s="16"/>
       <c r="AJ72" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6</v>
       </c>
       <c r="AK72" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL72" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL72" s="16">
+        <f t="shared" si="28"/>
+        <v>2.7829999999999999</v>
+      </c>
       <c r="AM72" s="16"/>
       <c r="AN72" s="16"/>
       <c r="AO72" s="16"/>
@@ -10018,11 +10223,11 @@
         <v>74</v>
       </c>
       <c r="L73" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-21</v>
       </c>
       <c r="M73" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>53</v>
       </c>
       <c r="N73" s="16"/>
@@ -10031,7 +10236,7 @@
       </c>
       <c r="P73" s="16"/>
       <c r="Q73" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10.6</v>
       </c>
       <c r="R73" s="4">
@@ -10039,21 +10244,21 @@
         <v>30</v>
       </c>
       <c r="S73" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="T73" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>30</v>
       </c>
       <c r="U73" s="4"/>
       <c r="V73" s="21"/>
       <c r="W73" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X73" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12.169811320754718</v>
       </c>
       <c r="Y73" s="16">
@@ -10090,14 +10295,17 @@
         <v>77</v>
       </c>
       <c r="AJ73" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.1000000000000014</v>
       </c>
       <c r="AK73" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL73" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL73" s="16">
+        <f t="shared" si="28"/>
+        <v>2.8620000000000001</v>
+      </c>
       <c r="AM73" s="16"/>
       <c r="AN73" s="16"/>
       <c r="AO73" s="16"/>
@@ -10145,11 +10353,11 @@
         <v>119</v>
       </c>
       <c r="L74" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-55</v>
       </c>
       <c r="M74" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>64</v>
       </c>
       <c r="N74" s="16"/>
@@ -10158,28 +10366,28 @@
       </c>
       <c r="P74" s="16"/>
       <c r="Q74" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.8</v>
       </c>
       <c r="R74" s="4">
         <v>8</v>
       </c>
       <c r="S74" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8</v>
       </c>
       <c r="T74" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8</v>
       </c>
       <c r="U74" s="4"/>
       <c r="V74" s="21"/>
       <c r="W74" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15.46875</v>
       </c>
       <c r="X74" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.84375</v>
       </c>
       <c r="Y74" s="16">
@@ -10214,14 +10422,17 @@
       </c>
       <c r="AI74" s="16"/>
       <c r="AJ74" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.4</v>
       </c>
       <c r="AK74" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL74" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL74" s="16">
+        <f t="shared" si="28"/>
+        <v>3.84</v>
+      </c>
       <c r="AM74" s="16"/>
       <c r="AN74" s="16"/>
       <c r="AO74" s="16"/>
@@ -10270,11 +10481,11 @@
         <v>1683</v>
       </c>
       <c r="L75" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-250</v>
       </c>
       <c r="M75" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1353</v>
       </c>
       <c r="N75" s="16">
@@ -10287,7 +10498,7 @@
         <v>1184</v>
       </c>
       <c r="Q75" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>270.60000000000002</v>
       </c>
       <c r="R75" s="4">
@@ -10295,11 +10506,11 @@
         <v>1545.0000000000005</v>
       </c>
       <c r="S75" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1545</v>
       </c>
       <c r="T75" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>772</v>
       </c>
       <c r="U75" s="4">
@@ -10308,11 +10519,11 @@
       </c>
       <c r="V75" s="21"/>
       <c r="W75" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X75" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.2904656319290453</v>
       </c>
       <c r="Y75" s="16">
@@ -10347,14 +10558,17 @@
       </c>
       <c r="AI75" s="16"/>
       <c r="AJ75" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>316.52</v>
       </c>
       <c r="AK75" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>316.93</v>
       </c>
-      <c r="AL75" s="16"/>
+      <c r="AL75" s="16">
+        <f t="shared" si="28"/>
+        <v>110.946</v>
+      </c>
       <c r="AM75" s="16"/>
       <c r="AN75" s="16"/>
       <c r="AO75" s="16"/>
@@ -10400,11 +10614,11 @@
         <v>9</v>
       </c>
       <c r="L76" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-8</v>
       </c>
       <c r="M76" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="N76" s="8"/>
@@ -10413,26 +10627,26 @@
       </c>
       <c r="P76" s="8"/>
       <c r="Q76" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2</v>
       </c>
       <c r="R76" s="10"/>
       <c r="S76" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T76" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U76" s="4"/>
       <c r="V76" s="22"/>
       <c r="W76" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X76" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Y76" s="8">
@@ -10467,14 +10681,17 @@
       </c>
       <c r="AI76" s="8"/>
       <c r="AJ76" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK76" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL76" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL76" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM76" s="16"/>
       <c r="AN76" s="16"/>
       <c r="AO76" s="16"/>
@@ -10523,11 +10740,11 @@
         <v>583.20799999999997</v>
       </c>
       <c r="L77" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-16.337999999999965</v>
       </c>
       <c r="M77" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>338.33199999999999</v>
       </c>
       <c r="N77" s="17">
@@ -10539,7 +10756,7 @@
       </c>
       <c r="P77" s="16"/>
       <c r="Q77" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>67.666399999999996</v>
       </c>
       <c r="R77" s="4">
@@ -10551,7 +10768,7 @@
         <v>488</v>
       </c>
       <c r="T77" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>244</v>
       </c>
       <c r="U77" s="4">
@@ -10562,11 +10779,11 @@
         <v>100</v>
       </c>
       <c r="W77" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>16.483779246420678</v>
       </c>
       <c r="X77" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.271928165234149</v>
       </c>
       <c r="Y77" s="16">
@@ -10601,14 +10818,17 @@
       </c>
       <c r="AI77" s="16"/>
       <c r="AJ77" s="16">
-        <f t="shared" si="25"/>
-        <v>244</v>
-      </c>
-      <c r="AK77" s="16">
         <f t="shared" si="26"/>
         <v>244</v>
       </c>
-      <c r="AL77" s="16"/>
+      <c r="AK77" s="16">
+        <f t="shared" si="27"/>
+        <v>244</v>
+      </c>
+      <c r="AL77" s="16">
+        <f t="shared" si="28"/>
+        <v>67.666399999999996</v>
+      </c>
       <c r="AM77" s="16"/>
       <c r="AN77" s="16"/>
       <c r="AO77" s="16"/>
@@ -10656,11 +10876,11 @@
         <v>58</v>
       </c>
       <c r="L78" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-11</v>
       </c>
       <c r="M78" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>47</v>
       </c>
       <c r="N78" s="16"/>
@@ -10669,7 +10889,7 @@
       </c>
       <c r="P78" s="16"/>
       <c r="Q78" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.4</v>
       </c>
       <c r="R78" s="4">
@@ -10677,21 +10897,21 @@
         <v>51</v>
       </c>
       <c r="S78" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>51</v>
       </c>
       <c r="T78" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>51</v>
       </c>
       <c r="U78" s="4"/>
       <c r="V78" s="21"/>
       <c r="W78" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X78" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.5744680851063819</v>
       </c>
       <c r="Y78" s="16">
@@ -10726,14 +10946,17 @@
       </c>
       <c r="AI78" s="16"/>
       <c r="AJ78" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.849999999999998</v>
       </c>
       <c r="AK78" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL78" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL78" s="16">
+        <f t="shared" si="28"/>
+        <v>3.29</v>
+      </c>
       <c r="AM78" s="16"/>
       <c r="AN78" s="16"/>
       <c r="AO78" s="16"/>
@@ -10771,11 +10994,11 @@
         <v>1.5</v>
       </c>
       <c r="L79" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1.5</v>
       </c>
       <c r="M79" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N79" s="8"/>
@@ -10784,26 +11007,26 @@
       </c>
       <c r="P79" s="8"/>
       <c r="Q79" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R79" s="10"/>
       <c r="S79" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T79" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U79" s="4"/>
       <c r="V79" s="22"/>
       <c r="W79" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X79" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y79" s="8">
@@ -10840,14 +11063,17 @@
         <v>134</v>
       </c>
       <c r="AJ79" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK79" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL79" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL79" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM79" s="16"/>
       <c r="AN79" s="16"/>
       <c r="AO79" s="16"/>
@@ -10895,11 +11121,11 @@
         <v>884</v>
       </c>
       <c r="L80" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-272</v>
       </c>
       <c r="M80" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>612</v>
       </c>
       <c r="N80" s="16"/>
@@ -10910,7 +11136,7 @@
         <v>700</v>
       </c>
       <c r="Q80" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>122.4</v>
       </c>
       <c r="R80" s="4">
@@ -10918,11 +11144,11 @@
         <v>415</v>
       </c>
       <c r="S80" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>415</v>
       </c>
       <c r="T80" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>207</v>
       </c>
       <c r="U80" s="4">
@@ -10931,11 +11157,11 @@
       </c>
       <c r="V80" s="21"/>
       <c r="W80" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X80" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.609477124183005</v>
       </c>
       <c r="Y80" s="16">
@@ -10972,14 +11198,17 @@
         <v>136</v>
       </c>
       <c r="AJ80" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>84.86999999999999</v>
       </c>
       <c r="AK80" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>85.28</v>
       </c>
-      <c r="AL80" s="16"/>
+      <c r="AL80" s="16">
+        <f t="shared" si="28"/>
+        <v>50.183999999999997</v>
+      </c>
       <c r="AM80" s="16"/>
       <c r="AN80" s="16"/>
       <c r="AO80" s="16"/>
@@ -11025,11 +11254,11 @@
         <v>140.5</v>
       </c>
       <c r="L81" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-11.152999999999992</v>
       </c>
       <c r="M81" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>129.34700000000001</v>
       </c>
       <c r="N81" s="16"/>
@@ -11040,7 +11269,7 @@
         <v>102</v>
       </c>
       <c r="Q81" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>25.869400000000002</v>
       </c>
       <c r="R81" s="4">
@@ -11048,21 +11277,21 @@
         <v>184.04100000000005</v>
       </c>
       <c r="S81" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>184</v>
       </c>
       <c r="T81" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>184</v>
       </c>
       <c r="U81" s="4"/>
       <c r="V81" s="21"/>
       <c r="W81" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14.99841511592847</v>
       </c>
       <c r="X81" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.8857646485809481</v>
       </c>
       <c r="Y81" s="16">
@@ -11097,14 +11326,17 @@
       </c>
       <c r="AI81" s="16"/>
       <c r="AJ81" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>184</v>
       </c>
       <c r="AK81" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL81" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL81" s="16">
+        <f t="shared" si="28"/>
+        <v>25.869400000000002</v>
+      </c>
       <c r="AM81" s="16"/>
       <c r="AN81" s="16"/>
       <c r="AO81" s="16"/>
@@ -11152,11 +11384,11 @@
         <v>156</v>
       </c>
       <c r="L82" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-9</v>
       </c>
       <c r="M82" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>129</v>
       </c>
       <c r="N82" s="16">
@@ -11167,7 +11399,7 @@
       </c>
       <c r="P82" s="16"/>
       <c r="Q82" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>25.8</v>
       </c>
       <c r="R82" s="4">
@@ -11175,11 +11407,11 @@
         <v>216.2</v>
       </c>
       <c r="S82" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>216</v>
       </c>
       <c r="T82" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>108</v>
       </c>
       <c r="U82" s="4">
@@ -11188,11 +11420,11 @@
       </c>
       <c r="V82" s="21"/>
       <c r="W82" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>13.992248062015504</v>
       </c>
       <c r="X82" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.6201550387596901</v>
       </c>
       <c r="Y82" s="16">
@@ -11227,14 +11459,17 @@
       </c>
       <c r="AI82" s="16"/>
       <c r="AJ82" s="16">
-        <f t="shared" si="25"/>
-        <v>32.4</v>
-      </c>
-      <c r="AK82" s="16">
         <f t="shared" si="26"/>
         <v>32.4</v>
       </c>
-      <c r="AL82" s="16"/>
+      <c r="AK82" s="16">
+        <f t="shared" si="27"/>
+        <v>32.4</v>
+      </c>
+      <c r="AL82" s="16">
+        <f t="shared" si="28"/>
+        <v>7.74</v>
+      </c>
       <c r="AM82" s="16"/>
       <c r="AN82" s="16"/>
       <c r="AO82" s="16"/>
@@ -11276,11 +11511,11 @@
         <v>29</v>
       </c>
       <c r="L83" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-9</v>
       </c>
       <c r="M83" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N83" s="8">
@@ -11289,26 +11524,26 @@
       <c r="O83" s="8"/>
       <c r="P83" s="8"/>
       <c r="Q83" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R83" s="10"/>
       <c r="S83" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T83" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U83" s="4"/>
       <c r="V83" s="22"/>
       <c r="W83" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X83" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y83" s="8">
@@ -11343,14 +11578,17 @@
       </c>
       <c r="AI83" s="8"/>
       <c r="AJ83" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK83" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL83" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL83" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM83" s="16"/>
       <c r="AN83" s="16"/>
       <c r="AO83" s="16"/>
@@ -11398,11 +11636,11 @@
         <v>214</v>
       </c>
       <c r="L84" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-5</v>
       </c>
       <c r="M84" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>179</v>
       </c>
       <c r="N84" s="16">
@@ -11415,26 +11653,26 @@
         <v>245</v>
       </c>
       <c r="Q84" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>35.799999999999997</v>
       </c>
       <c r="R84" s="4"/>
       <c r="S84" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T84" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U84" s="4"/>
       <c r="V84" s="21"/>
       <c r="W84" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>17.597765363128492</v>
       </c>
       <c r="X84" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>17.597765363128492</v>
       </c>
       <c r="Y84" s="16">
@@ -11469,14 +11707,17 @@
       </c>
       <c r="AI84" s="16"/>
       <c r="AJ84" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK84" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL84" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL84" s="16">
+        <f t="shared" si="28"/>
+        <v>6.4439999999999991</v>
+      </c>
       <c r="AM84" s="16"/>
       <c r="AN84" s="16"/>
       <c r="AO84" s="16"/>
@@ -11518,11 +11759,11 @@
         <v>12</v>
       </c>
       <c r="L85" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M85" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N85" s="8">
@@ -11531,26 +11772,26 @@
       <c r="O85" s="8"/>
       <c r="P85" s="8"/>
       <c r="Q85" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R85" s="10"/>
       <c r="S85" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T85" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U85" s="4"/>
       <c r="V85" s="22"/>
       <c r="W85" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X85" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y85" s="8">
@@ -11585,14 +11826,17 @@
       </c>
       <c r="AI85" s="8"/>
       <c r="AJ85" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK85" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL85" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL85" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM85" s="16"/>
       <c r="AN85" s="16"/>
       <c r="AO85" s="16"/>
@@ -11638,13 +11882,13 @@
         <v>32</v>
       </c>
       <c r="L86" s="8">
-        <f t="shared" si="20"/>
-        <v>-3</v>
-      </c>
-      <c r="M86" s="8">
         <f t="shared" si="21"/>
         <v>-3</v>
       </c>
+      <c r="M86" s="8">
+        <f t="shared" si="22"/>
+        <v>-3</v>
+      </c>
       <c r="N86" s="8">
         <v>32</v>
       </c>
@@ -11653,26 +11897,26 @@
       </c>
       <c r="P86" s="8"/>
       <c r="Q86" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.6</v>
       </c>
       <c r="R86" s="10"/>
       <c r="S86" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T86" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U86" s="4"/>
       <c r="V86" s="22"/>
       <c r="W86" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X86" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Y86" s="8">
@@ -11707,14 +11951,17 @@
       </c>
       <c r="AI86" s="8"/>
       <c r="AJ86" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK86" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL86" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL86" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM86" s="16"/>
       <c r="AN86" s="16"/>
       <c r="AO86" s="16"/>
@@ -11752,11 +11999,11 @@
         <v>1</v>
       </c>
       <c r="L87" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="M87" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N87" s="8"/>
@@ -11765,26 +12012,26 @@
       </c>
       <c r="P87" s="8"/>
       <c r="Q87" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R87" s="10"/>
       <c r="S87" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T87" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U87" s="4"/>
       <c r="V87" s="22"/>
       <c r="W87" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X87" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y87" s="8">
@@ -11821,14 +12068,17 @@
         <v>134</v>
       </c>
       <c r="AJ87" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK87" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL87" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL87" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM87" s="16"/>
       <c r="AN87" s="16"/>
       <c r="AO87" s="16"/>
@@ -11876,11 +12126,11 @@
         <v>999</v>
       </c>
       <c r="L88" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-116</v>
       </c>
       <c r="M88" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>827</v>
       </c>
       <c r="N88" s="16">
@@ -11893,7 +12143,7 @@
         <v>463</v>
       </c>
       <c r="Q88" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>165.4</v>
       </c>
       <c r="R88" s="4">
@@ -11901,11 +12151,11 @@
         <v>1076</v>
       </c>
       <c r="S88" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1076</v>
       </c>
       <c r="T88" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>538</v>
       </c>
       <c r="U88" s="4">
@@ -11914,11 +12164,11 @@
       </c>
       <c r="V88" s="21"/>
       <c r="W88" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X88" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.4945586457073752</v>
       </c>
       <c r="Y88" s="16">
@@ -11953,14 +12203,17 @@
       </c>
       <c r="AI88" s="16"/>
       <c r="AJ88" s="16">
-        <f t="shared" si="25"/>
-        <v>188.29999999999998</v>
-      </c>
-      <c r="AK88" s="16">
         <f t="shared" si="26"/>
         <v>188.29999999999998</v>
       </c>
-      <c r="AL88" s="16"/>
+      <c r="AK88" s="16">
+        <f t="shared" si="27"/>
+        <v>188.29999999999998</v>
+      </c>
+      <c r="AL88" s="16">
+        <f t="shared" si="28"/>
+        <v>57.89</v>
+      </c>
       <c r="AM88" s="16"/>
       <c r="AN88" s="16"/>
       <c r="AO88" s="16"/>
@@ -11996,11 +12249,11 @@
       <c r="J89" s="16"/>
       <c r="K89" s="16"/>
       <c r="L89" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M89" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N89" s="16"/>
@@ -12009,26 +12262,26 @@
       </c>
       <c r="P89" s="16"/>
       <c r="Q89" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R89" s="4"/>
       <c r="S89" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T89" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U89" s="4"/>
       <c r="V89" s="21"/>
       <c r="W89" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X89" s="16" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y89" s="16">
@@ -12065,14 +12318,17 @@
         <v>100</v>
       </c>
       <c r="AJ89" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK89" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL89" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL89" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM89" s="16"/>
       <c r="AN89" s="16"/>
       <c r="AO89" s="16"/>
@@ -12120,11 +12376,11 @@
         <v>290.82600000000002</v>
       </c>
       <c r="L90" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>7.4599999999999795</v>
       </c>
       <c r="M90" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>265.95999999999998</v>
       </c>
       <c r="N90" s="16">
@@ -12135,7 +12391,7 @@
       </c>
       <c r="P90" s="16"/>
       <c r="Q90" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>53.191999999999993</v>
       </c>
       <c r="R90" s="4">
@@ -12143,11 +12399,11 @@
         <v>423.72099999999989</v>
       </c>
       <c r="S90" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>424</v>
       </c>
       <c r="T90" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>212</v>
       </c>
       <c r="U90" s="4">
@@ -12156,11 +12412,11 @@
       </c>
       <c r="V90" s="21"/>
       <c r="W90" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>12.005245149646564</v>
       </c>
       <c r="X90" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.0341216724319455</v>
       </c>
       <c r="Y90" s="16">
@@ -12195,14 +12451,17 @@
       </c>
       <c r="AI90" s="16"/>
       <c r="AJ90" s="16">
-        <f t="shared" si="25"/>
-        <v>212</v>
-      </c>
-      <c r="AK90" s="16">
         <f t="shared" si="26"/>
         <v>212</v>
       </c>
-      <c r="AL90" s="16"/>
+      <c r="AK90" s="16">
+        <f t="shared" si="27"/>
+        <v>212</v>
+      </c>
+      <c r="AL90" s="16">
+        <f t="shared" si="28"/>
+        <v>53.191999999999993</v>
+      </c>
       <c r="AM90" s="16"/>
       <c r="AN90" s="16"/>
       <c r="AO90" s="16"/>
@@ -12244,11 +12503,11 @@
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M91" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N91" s="8"/>
@@ -12257,26 +12516,26 @@
       </c>
       <c r="P91" s="8"/>
       <c r="Q91" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R91" s="10"/>
       <c r="S91" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T91" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U91" s="4"/>
       <c r="V91" s="22"/>
       <c r="W91" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X91" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y91" s="8">
@@ -12313,14 +12572,17 @@
         <v>148</v>
       </c>
       <c r="AJ91" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK91" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL91" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL91" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM91" s="16"/>
       <c r="AN91" s="16"/>
       <c r="AO91" s="16"/>
@@ -12368,11 +12630,11 @@
         <v>390.37200000000001</v>
       </c>
       <c r="L92" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>20.966999999999985</v>
       </c>
       <c r="M92" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>360.96699999999998</v>
       </c>
       <c r="N92" s="16">
@@ -12383,7 +12645,7 @@
       </c>
       <c r="P92" s="16"/>
       <c r="Q92" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>72.193399999999997</v>
       </c>
       <c r="R92" s="4">
@@ -12391,24 +12653,24 @@
         <v>596.82619999999997</v>
       </c>
       <c r="S92" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>597</v>
       </c>
       <c r="T92" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>298</v>
       </c>
       <c r="U92" s="4">
-        <f t="shared" ref="U92:U93" si="29">ROUND(S92*$U$1,0)</f>
+        <f t="shared" ref="U92:U93" si="31">ROUND(S92*$U$1,0)</f>
         <v>299</v>
       </c>
       <c r="V92" s="21"/>
       <c r="W92" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>13.00240742228514</v>
       </c>
       <c r="X92" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.7329534278756782</v>
       </c>
       <c r="Y92" s="16">
@@ -12443,14 +12705,17 @@
       </c>
       <c r="AI92" s="16"/>
       <c r="AJ92" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>298</v>
       </c>
       <c r="AK92" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>299</v>
       </c>
-      <c r="AL92" s="16"/>
+      <c r="AL92" s="16">
+        <f t="shared" si="28"/>
+        <v>72.193399999999997</v>
+      </c>
       <c r="AM92" s="16"/>
       <c r="AN92" s="16"/>
       <c r="AO92" s="16"/>
@@ -12498,11 +12763,11 @@
         <v>1090</v>
       </c>
       <c r="L93" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-172</v>
       </c>
       <c r="M93" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>918</v>
       </c>
       <c r="N93" s="16"/>
@@ -12513,32 +12778,32 @@
         <v>208</v>
       </c>
       <c r="Q93" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>183.6</v>
       </c>
       <c r="R93" s="4">
-        <f t="shared" ref="R93:R96" si="30">15*Q93-P93-O93-F93</f>
+        <f t="shared" ref="R93:R96" si="32">15*Q93-P93-O93-F93</f>
         <v>1474</v>
       </c>
       <c r="S93" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1474</v>
       </c>
       <c r="T93" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>737</v>
       </c>
       <c r="U93" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>737</v>
       </c>
       <c r="V93" s="21"/>
       <c r="W93" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X93" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.9716775599128544</v>
       </c>
       <c r="Y93" s="16">
@@ -12573,14 +12838,17 @@
       </c>
       <c r="AI93" s="16"/>
       <c r="AJ93" s="16">
-        <f t="shared" si="25"/>
-        <v>257.95</v>
-      </c>
-      <c r="AK93" s="16">
         <f t="shared" si="26"/>
         <v>257.95</v>
       </c>
-      <c r="AL93" s="16"/>
+      <c r="AK93" s="16">
+        <f t="shared" si="27"/>
+        <v>257.95</v>
+      </c>
+      <c r="AL93" s="16">
+        <f t="shared" si="28"/>
+        <v>64.259999999999991</v>
+      </c>
       <c r="AM93" s="16"/>
       <c r="AN93" s="16"/>
       <c r="AO93" s="16"/>
@@ -12628,11 +12896,11 @@
         <v>183</v>
       </c>
       <c r="L94" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-40</v>
       </c>
       <c r="M94" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>125</v>
       </c>
       <c r="N94" s="16">
@@ -12643,29 +12911,29 @@
       </c>
       <c r="P94" s="16"/>
       <c r="Q94" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>25</v>
       </c>
       <c r="R94" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>183</v>
       </c>
       <c r="S94" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>183</v>
       </c>
       <c r="T94" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>183</v>
       </c>
       <c r="U94" s="4"/>
       <c r="V94" s="21"/>
       <c r="W94" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X94" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.68</v>
       </c>
       <c r="Y94" s="16">
@@ -12700,14 +12968,17 @@
       </c>
       <c r="AI94" s="16"/>
       <c r="AJ94" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>54.9</v>
       </c>
       <c r="AK94" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL94" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL94" s="16">
+        <f t="shared" si="28"/>
+        <v>7.5</v>
+      </c>
       <c r="AM94" s="16"/>
       <c r="AN94" s="16"/>
       <c r="AO94" s="16"/>
@@ -12755,11 +13026,11 @@
         <v>79</v>
       </c>
       <c r="L95" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-30</v>
       </c>
       <c r="M95" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>49</v>
       </c>
       <c r="N95" s="16"/>
@@ -12768,29 +13039,29 @@
       </c>
       <c r="P95" s="16"/>
       <c r="Q95" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="R95" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>59</v>
       </c>
       <c r="S95" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>59</v>
       </c>
       <c r="T95" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>59</v>
       </c>
       <c r="U95" s="4"/>
       <c r="V95" s="21"/>
       <c r="W95" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14.999999999999998</v>
       </c>
       <c r="X95" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.9795918367346932</v>
       </c>
       <c r="Y95" s="16">
@@ -12825,14 +13096,17 @@
       </c>
       <c r="AI95" s="16"/>
       <c r="AJ95" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.7</v>
       </c>
       <c r="AK95" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL95" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL95" s="16">
+        <f t="shared" si="28"/>
+        <v>2.94</v>
+      </c>
       <c r="AM95" s="16"/>
       <c r="AN95" s="16"/>
       <c r="AO95" s="16"/>
@@ -12880,11 +13154,11 @@
         <v>150</v>
       </c>
       <c r="L96" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-27</v>
       </c>
       <c r="M96" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>99</v>
       </c>
       <c r="N96" s="16">
@@ -12895,29 +13169,29 @@
       </c>
       <c r="P96" s="16"/>
       <c r="Q96" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19.8</v>
       </c>
       <c r="R96" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>76</v>
       </c>
       <c r="S96" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>76</v>
       </c>
       <c r="T96" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>76</v>
       </c>
       <c r="U96" s="4"/>
       <c r="V96" s="21"/>
       <c r="W96" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X96" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.161616161616161</v>
       </c>
       <c r="Y96" s="16">
@@ -12952,14 +13226,17 @@
       </c>
       <c r="AI96" s="16"/>
       <c r="AJ96" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>21.28</v>
       </c>
       <c r="AK96" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL96" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL96" s="16">
+        <f t="shared" si="28"/>
+        <v>5.5440000000000005</v>
+      </c>
       <c r="AM96" s="16"/>
       <c r="AN96" s="16"/>
       <c r="AO96" s="16"/>
@@ -13007,11 +13284,11 @@
         <v>728</v>
       </c>
       <c r="L97" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-316</v>
       </c>
       <c r="M97" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>380</v>
       </c>
       <c r="N97" s="16">
@@ -13024,7 +13301,7 @@
         <v>450</v>
       </c>
       <c r="Q97" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>76</v>
       </c>
       <c r="R97" s="4">
@@ -13032,21 +13309,21 @@
         <v>53</v>
       </c>
       <c r="S97" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>53</v>
       </c>
       <c r="T97" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>53</v>
       </c>
       <c r="U97" s="4"/>
       <c r="V97" s="21"/>
       <c r="W97" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14</v>
       </c>
       <c r="X97" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>13.302631578947368</v>
       </c>
       <c r="Y97" s="16">
@@ -13083,14 +13360,17 @@
         <v>155</v>
       </c>
       <c r="AJ97" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>14.840000000000002</v>
       </c>
       <c r="AK97" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL97" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL97" s="16">
+        <f t="shared" si="28"/>
+        <v>21.28</v>
+      </c>
       <c r="AM97" s="16"/>
       <c r="AN97" s="16"/>
       <c r="AO97" s="16"/>
@@ -13136,11 +13416,11 @@
         <v>39</v>
       </c>
       <c r="L98" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-40</v>
       </c>
       <c r="M98" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>-1</v>
       </c>
       <c r="N98" s="8"/>
@@ -13149,26 +13429,26 @@
       </c>
       <c r="P98" s="8"/>
       <c r="Q98" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.2</v>
       </c>
       <c r="R98" s="10"/>
       <c r="S98" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T98" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U98" s="4"/>
       <c r="V98" s="22"/>
       <c r="W98" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X98" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Y98" s="8">
@@ -13205,14 +13485,17 @@
         <v>90</v>
       </c>
       <c r="AJ98" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK98" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL98" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL98" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM98" s="16"/>
       <c r="AN98" s="16"/>
       <c r="AO98" s="16"/>
@@ -13260,11 +13543,11 @@
         <v>306</v>
       </c>
       <c r="L99" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-95</v>
       </c>
       <c r="M99" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>211</v>
       </c>
       <c r="N99" s="16"/>
@@ -13275,7 +13558,7 @@
         <v>141</v>
       </c>
       <c r="Q99" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>42.2</v>
       </c>
       <c r="R99" s="4">
@@ -13287,22 +13570,22 @@
         <v>280</v>
       </c>
       <c r="T99" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>140</v>
       </c>
       <c r="U99" s="4">
-        <f t="shared" ref="U99:U100" si="31">ROUND(S99*$U$1,0)</f>
+        <f t="shared" ref="U99:U100" si="33">ROUND(S99*$U$1,0)</f>
         <v>140</v>
       </c>
       <c r="V99" s="21">
         <v>40</v>
       </c>
       <c r="W99" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15.947867298578197</v>
       </c>
       <c r="X99" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.3127962085308056</v>
       </c>
       <c r="Y99" s="16">
@@ -13337,14 +13620,17 @@
       </c>
       <c r="AI99" s="16"/>
       <c r="AJ99" s="16">
-        <f t="shared" si="25"/>
-        <v>39.200000000000003</v>
-      </c>
-      <c r="AK99" s="16">
         <f t="shared" si="26"/>
         <v>39.200000000000003</v>
       </c>
-      <c r="AL99" s="16"/>
+      <c r="AK99" s="16">
+        <f t="shared" si="27"/>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="AL99" s="16">
+        <f t="shared" si="28"/>
+        <v>11.816000000000003</v>
+      </c>
       <c r="AM99" s="16"/>
       <c r="AN99" s="16"/>
       <c r="AO99" s="16"/>
@@ -13390,11 +13676,11 @@
         <v>528</v>
       </c>
       <c r="L100" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-132</v>
       </c>
       <c r="M100" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>360</v>
       </c>
       <c r="N100" s="16">
@@ -13407,7 +13693,7 @@
         <v>279</v>
       </c>
       <c r="Q100" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>72</v>
       </c>
       <c r="R100" s="4">
@@ -13415,24 +13701,24 @@
         <v>522</v>
       </c>
       <c r="S100" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>522</v>
       </c>
       <c r="T100" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>261</v>
       </c>
       <c r="U100" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>261</v>
       </c>
       <c r="V100" s="21"/>
       <c r="W100" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X100" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.75</v>
       </c>
       <c r="Y100" s="16">
@@ -13467,14 +13753,17 @@
       </c>
       <c r="AI100" s="16"/>
       <c r="AJ100" s="16">
-        <f t="shared" si="25"/>
-        <v>104.4</v>
-      </c>
-      <c r="AK100" s="16">
         <f t="shared" si="26"/>
         <v>104.4</v>
       </c>
-      <c r="AL100" s="16"/>
+      <c r="AK100" s="16">
+        <f t="shared" si="27"/>
+        <v>104.4</v>
+      </c>
+      <c r="AL100" s="16">
+        <f t="shared" si="28"/>
+        <v>28.8</v>
+      </c>
       <c r="AM100" s="16"/>
       <c r="AN100" s="16"/>
       <c r="AO100" s="16"/>
@@ -13516,11 +13805,11 @@
         <v>31.652000000000001</v>
       </c>
       <c r="L101" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M101" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="N101" s="8">
@@ -13529,26 +13818,26 @@
       <c r="O101" s="8"/>
       <c r="P101" s="8"/>
       <c r="Q101" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="R101" s="10"/>
       <c r="S101" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T101" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U101" s="4"/>
       <c r="V101" s="22"/>
       <c r="W101" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X101" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y101" s="8">
@@ -13583,14 +13872,17 @@
       </c>
       <c r="AI101" s="8"/>
       <c r="AJ101" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK101" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL101" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL101" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM101" s="16"/>
       <c r="AN101" s="16"/>
       <c r="AO101" s="16"/>
@@ -13636,11 +13928,11 @@
         <v>7</v>
       </c>
       <c r="L102" s="8">
-        <f t="shared" ref="L102:L133" si="32">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="34">E102-K102</f>
         <v>-9</v>
       </c>
       <c r="M102" s="8">
-        <f t="shared" ref="M102:M133" si="33">E102-N102</f>
+        <f t="shared" ref="M102:M133" si="35">E102-N102</f>
         <v>-2</v>
       </c>
       <c r="N102" s="8"/>
@@ -13649,26 +13941,26 @@
       </c>
       <c r="P102" s="8"/>
       <c r="Q102" s="8">
-        <f t="shared" ref="Q102:Q133" si="34">M102/5</f>
+        <f t="shared" ref="Q102:Q133" si="36">M102/5</f>
         <v>-0.4</v>
       </c>
       <c r="R102" s="10"/>
       <c r="S102" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T102" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U102" s="4"/>
       <c r="V102" s="22"/>
       <c r="W102" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X102" s="8">
-        <f t="shared" ref="X102:X133" si="35">(F102+O102+P102)/Q102</f>
+        <f t="shared" ref="X102:X133" si="37">(F102+O102+P102)/Q102</f>
         <v>0</v>
       </c>
       <c r="Y102" s="8">
@@ -13703,14 +13995,17 @@
       </c>
       <c r="AI102" s="8"/>
       <c r="AJ102" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK102" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL102" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL102" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM102" s="16"/>
       <c r="AN102" s="16"/>
       <c r="AO102" s="16"/>
@@ -13756,11 +14051,11 @@
         <v>11</v>
       </c>
       <c r="L103" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-9</v>
       </c>
       <c r="M103" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="N103" s="8"/>
@@ -13769,26 +14064,26 @@
       </c>
       <c r="P103" s="8"/>
       <c r="Q103" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.4</v>
       </c>
       <c r="R103" s="10"/>
       <c r="S103" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T103" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U103" s="4"/>
       <c r="V103" s="22"/>
       <c r="W103" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X103" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Y103" s="8">
@@ -13825,14 +14120,17 @@
         <v>90</v>
       </c>
       <c r="AJ103" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK103" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL103" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL103" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM103" s="16"/>
       <c r="AN103" s="16"/>
       <c r="AO103" s="16"/>
@@ -13878,11 +14176,11 @@
         <v>1</v>
       </c>
       <c r="L104" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1</v>
       </c>
       <c r="M104" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N104" s="8"/>
@@ -13891,26 +14189,26 @@
       </c>
       <c r="P104" s="8"/>
       <c r="Q104" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R104" s="10"/>
       <c r="S104" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T104" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U104" s="4"/>
       <c r="V104" s="22"/>
       <c r="W104" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X104" s="8" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y104" s="8">
@@ -13947,14 +14245,17 @@
         <v>163</v>
       </c>
       <c r="AJ104" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK104" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL104" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL104" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM104" s="16"/>
       <c r="AN104" s="16"/>
       <c r="AO104" s="16"/>
@@ -14002,11 +14303,11 @@
         <v>145.31200000000001</v>
       </c>
       <c r="L105" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>3.4170000000000016</v>
       </c>
       <c r="M105" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>148.72900000000001</v>
       </c>
       <c r="N105" s="16"/>
@@ -14015,7 +14316,7 @@
       </c>
       <c r="P105" s="16"/>
       <c r="Q105" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>29.745800000000003</v>
       </c>
       <c r="R105" s="4">
@@ -14027,7 +14328,7 @@
         <v>116</v>
       </c>
       <c r="T105" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>116</v>
       </c>
       <c r="U105" s="4"/>
@@ -14035,11 +14336,11 @@
         <v>-100</v>
       </c>
       <c r="W105" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>11.622951811684338</v>
       </c>
       <c r="X105" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>7.723241600494859</v>
       </c>
       <c r="Y105" s="16">
@@ -14076,14 +14377,17 @@
         <v>77</v>
       </c>
       <c r="AJ105" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>116</v>
       </c>
       <c r="AK105" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL105" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL105" s="16">
+        <f t="shared" si="28"/>
+        <v>29.745800000000003</v>
+      </c>
       <c r="AM105" s="16"/>
       <c r="AN105" s="16"/>
       <c r="AO105" s="16"/>
@@ -14125,11 +14429,11 @@
         <v>7</v>
       </c>
       <c r="L106" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M106" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N106" s="8">
@@ -14138,26 +14442,26 @@
       <c r="O106" s="8"/>
       <c r="P106" s="8"/>
       <c r="Q106" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R106" s="10"/>
       <c r="S106" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T106" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U106" s="4"/>
       <c r="V106" s="22"/>
       <c r="W106" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X106" s="8" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y106" s="8">
@@ -14192,14 +14496,17 @@
       </c>
       <c r="AI106" s="8"/>
       <c r="AJ106" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK106" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL106" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL106" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM106" s="16"/>
       <c r="AN106" s="16"/>
       <c r="AO106" s="16"/>
@@ -14245,11 +14552,11 @@
         <v>27</v>
       </c>
       <c r="L107" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-10</v>
       </c>
       <c r="M107" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>17</v>
       </c>
       <c r="N107" s="16"/>
@@ -14258,7 +14565,7 @@
       </c>
       <c r="P107" s="16"/>
       <c r="Q107" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>3.4</v>
       </c>
       <c r="R107" s="4">
@@ -14266,21 +14573,21 @@
         <v>27.2</v>
       </c>
       <c r="S107" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>27</v>
       </c>
       <c r="T107" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>27</v>
       </c>
       <c r="U107" s="4"/>
       <c r="V107" s="21"/>
       <c r="W107" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.9411764705882355</v>
       </c>
       <c r="X107" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Y107" s="16">
@@ -14315,14 +14622,17 @@
       </c>
       <c r="AI107" s="16"/>
       <c r="AJ107" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.5600000000000005</v>
       </c>
       <c r="AK107" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL107" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL107" s="16">
+        <f t="shared" si="28"/>
+        <v>0.95200000000000007</v>
+      </c>
       <c r="AM107" s="16"/>
       <c r="AN107" s="16"/>
       <c r="AO107" s="16"/>
@@ -14370,11 +14680,11 @@
         <v>39</v>
       </c>
       <c r="L108" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-7</v>
       </c>
       <c r="M108" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N108" s="8">
@@ -14385,26 +14695,26 @@
       </c>
       <c r="P108" s="8"/>
       <c r="Q108" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R108" s="10"/>
       <c r="S108" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T108" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U108" s="4"/>
       <c r="V108" s="22"/>
       <c r="W108" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X108" s="8" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y108" s="8">
@@ -14439,14 +14749,17 @@
       </c>
       <c r="AI108" s="8"/>
       <c r="AJ108" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK108" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL108" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL108" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM108" s="16"/>
       <c r="AN108" s="16"/>
       <c r="AO108" s="16"/>
@@ -14488,11 +14801,11 @@
         <v>24</v>
       </c>
       <c r="L109" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M109" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N109" s="8">
@@ -14501,26 +14814,26 @@
       <c r="O109" s="8"/>
       <c r="P109" s="8"/>
       <c r="Q109" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R109" s="10"/>
       <c r="S109" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T109" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U109" s="4"/>
       <c r="V109" s="22"/>
       <c r="W109" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X109" s="8" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y109" s="8">
@@ -14555,14 +14868,17 @@
       </c>
       <c r="AI109" s="8"/>
       <c r="AJ109" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK109" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL109" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL109" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM109" s="16"/>
       <c r="AN109" s="16"/>
       <c r="AO109" s="16"/>
@@ -14604,11 +14920,11 @@
         <v>32</v>
       </c>
       <c r="L110" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M110" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N110" s="8">
@@ -14617,26 +14933,26 @@
       <c r="O110" s="8"/>
       <c r="P110" s="8"/>
       <c r="Q110" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R110" s="10"/>
       <c r="S110" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T110" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U110" s="4"/>
       <c r="V110" s="22"/>
       <c r="W110" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X110" s="8" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y110" s="8">
@@ -14671,14 +14987,17 @@
       </c>
       <c r="AI110" s="8"/>
       <c r="AJ110" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK110" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL110" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL110" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM110" s="16"/>
       <c r="AN110" s="16"/>
       <c r="AO110" s="16"/>
@@ -14724,11 +15043,11 @@
         <v>15</v>
       </c>
       <c r="L111" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-18</v>
       </c>
       <c r="M111" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-3</v>
       </c>
       <c r="N111" s="8"/>
@@ -14737,26 +15056,26 @@
       </c>
       <c r="P111" s="8"/>
       <c r="Q111" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.6</v>
       </c>
       <c r="R111" s="10"/>
       <c r="S111" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T111" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U111" s="4"/>
       <c r="V111" s="22"/>
       <c r="W111" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X111" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Y111" s="8">
@@ -14793,14 +15112,17 @@
         <v>90</v>
       </c>
       <c r="AJ111" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK111" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL111" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL111" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM111" s="16"/>
       <c r="AN111" s="16"/>
       <c r="AO111" s="16"/>
@@ -14848,11 +15170,11 @@
         <v>239</v>
       </c>
       <c r="L112" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-15</v>
       </c>
       <c r="M112" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>184</v>
       </c>
       <c r="N112" s="16">
@@ -14863,7 +15185,7 @@
       </c>
       <c r="P112" s="16"/>
       <c r="Q112" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>36.799999999999997</v>
       </c>
       <c r="R112" s="4">
@@ -14871,11 +15193,11 @@
         <v>202</v>
       </c>
       <c r="S112" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>202</v>
       </c>
       <c r="T112" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>101</v>
       </c>
       <c r="U112" s="4">
@@ -14884,11 +15206,11 @@
       </c>
       <c r="V112" s="21"/>
       <c r="W112" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15.000000000000002</v>
       </c>
       <c r="X112" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>9.5108695652173925</v>
       </c>
       <c r="Y112" s="16">
@@ -14923,14 +15245,17 @@
       </c>
       <c r="AI112" s="16"/>
       <c r="AJ112" s="16">
-        <f t="shared" si="25"/>
-        <v>12.12</v>
-      </c>
-      <c r="AK112" s="16">
         <f t="shared" si="26"/>
         <v>12.12</v>
       </c>
-      <c r="AL112" s="16"/>
+      <c r="AK112" s="16">
+        <f t="shared" si="27"/>
+        <v>12.12</v>
+      </c>
+      <c r="AL112" s="16">
+        <f t="shared" si="28"/>
+        <v>4.4159999999999995</v>
+      </c>
       <c r="AM112" s="16"/>
       <c r="AN112" s="16"/>
       <c r="AO112" s="16"/>
@@ -14972,11 +15297,11 @@
         <v>16</v>
       </c>
       <c r="L113" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M113" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N113" s="8">
@@ -14985,26 +15310,26 @@
       <c r="O113" s="8"/>
       <c r="P113" s="8"/>
       <c r="Q113" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R113" s="10"/>
       <c r="S113" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T113" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U113" s="4"/>
       <c r="V113" s="22"/>
       <c r="W113" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X113" s="8" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y113" s="8">
@@ -15039,14 +15364,17 @@
       </c>
       <c r="AI113" s="8"/>
       <c r="AJ113" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK113" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL113" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL113" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM113" s="16"/>
       <c r="AN113" s="16"/>
       <c r="AO113" s="16"/>
@@ -15094,11 +15422,11 @@
         <v>273</v>
       </c>
       <c r="L114" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-34</v>
       </c>
       <c r="M114" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>239</v>
       </c>
       <c r="N114" s="16"/>
@@ -15109,7 +15437,7 @@
         <v>155</v>
       </c>
       <c r="Q114" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>47.8</v>
       </c>
       <c r="R114" s="4">
@@ -15117,24 +15445,24 @@
         <v>358</v>
       </c>
       <c r="S114" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>358</v>
       </c>
       <c r="T114" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>179</v>
       </c>
       <c r="U114" s="4">
-        <f t="shared" ref="U114:U115" si="36">ROUND(S114*$U$1,0)</f>
+        <f t="shared" ref="U114:U115" si="38">ROUND(S114*$U$1,0)</f>
         <v>179</v>
       </c>
       <c r="V114" s="21"/>
       <c r="W114" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15.000000000000002</v>
       </c>
       <c r="X114" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>7.5104602510460259</v>
       </c>
       <c r="Y114" s="16">
@@ -15169,14 +15497,17 @@
       </c>
       <c r="AI114" s="16"/>
       <c r="AJ114" s="16">
-        <f t="shared" si="25"/>
-        <v>59.07</v>
-      </c>
-      <c r="AK114" s="16">
         <f t="shared" si="26"/>
         <v>59.07</v>
       </c>
-      <c r="AL114" s="16"/>
+      <c r="AK114" s="16">
+        <f t="shared" si="27"/>
+        <v>59.07</v>
+      </c>
+      <c r="AL114" s="16">
+        <f t="shared" si="28"/>
+        <v>15.773999999999999</v>
+      </c>
       <c r="AM114" s="16"/>
       <c r="AN114" s="16"/>
       <c r="AO114" s="16"/>
@@ -15224,11 +15555,11 @@
         <v>136</v>
       </c>
       <c r="L115" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-21</v>
       </c>
       <c r="M115" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>115</v>
       </c>
       <c r="N115" s="16"/>
@@ -15237,7 +15568,7 @@
       </c>
       <c r="P115" s="16"/>
       <c r="Q115" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>23</v>
       </c>
       <c r="R115" s="4">
@@ -15249,22 +15580,22 @@
         <v>380</v>
       </c>
       <c r="T115" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>190</v>
       </c>
       <c r="U115" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>190</v>
       </c>
       <c r="V115" s="21">
         <v>200</v>
       </c>
       <c r="W115" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>21.695652173913043</v>
       </c>
       <c r="X115" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>5.1739130434782608</v>
       </c>
       <c r="Y115" s="16">
@@ -15301,14 +15632,17 @@
         <v>77</v>
       </c>
       <c r="AJ115" s="16">
-        <f t="shared" si="25"/>
-        <v>28.5</v>
-      </c>
-      <c r="AK115" s="16">
         <f t="shared" si="26"/>
         <v>28.5</v>
       </c>
-      <c r="AL115" s="16"/>
+      <c r="AK115" s="16">
+        <f t="shared" si="27"/>
+        <v>28.5</v>
+      </c>
+      <c r="AL115" s="16">
+        <f t="shared" si="28"/>
+        <v>3.4499999999999997</v>
+      </c>
       <c r="AM115" s="16"/>
       <c r="AN115" s="16"/>
       <c r="AO115" s="16"/>
@@ -15354,11 +15688,11 @@
         <v>22</v>
       </c>
       <c r="L116" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-29</v>
       </c>
       <c r="M116" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-7</v>
       </c>
       <c r="N116" s="8"/>
@@ -15367,26 +15701,26 @@
       </c>
       <c r="P116" s="8"/>
       <c r="Q116" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-1.4</v>
       </c>
       <c r="R116" s="10"/>
       <c r="S116" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T116" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U116" s="4"/>
       <c r="V116" s="22"/>
       <c r="W116" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X116" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Y116" s="8">
@@ -15423,14 +15757,17 @@
         <v>90</v>
       </c>
       <c r="AJ116" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK116" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL116" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL116" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM116" s="16"/>
       <c r="AN116" s="16"/>
       <c r="AO116" s="16"/>
@@ -15478,11 +15815,11 @@
         <v>73</v>
       </c>
       <c r="L117" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-30</v>
       </c>
       <c r="M117" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>43</v>
       </c>
       <c r="N117" s="16"/>
@@ -15491,7 +15828,7 @@
       </c>
       <c r="P117" s="16"/>
       <c r="Q117" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.6</v>
       </c>
       <c r="R117" s="4">
@@ -15503,7 +15840,7 @@
         <v>113</v>
       </c>
       <c r="T117" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>113</v>
       </c>
       <c r="U117" s="4"/>
@@ -15511,11 +15848,11 @@
         <v>50</v>
       </c>
       <c r="W117" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>20.813953488372093</v>
       </c>
       <c r="X117" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>7.6744186046511631</v>
       </c>
       <c r="Y117" s="16">
@@ -15552,14 +15889,17 @@
         <v>77</v>
       </c>
       <c r="AJ117" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29.380000000000003</v>
       </c>
       <c r="AK117" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL117" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL117" s="16">
+        <f t="shared" si="28"/>
+        <v>2.2359999999999998</v>
+      </c>
       <c r="AM117" s="16"/>
       <c r="AN117" s="16"/>
       <c r="AO117" s="16"/>
@@ -15595,11 +15935,11 @@
       <c r="J118" s="12"/>
       <c r="K118" s="12"/>
       <c r="L118" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M118" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N118" s="12"/>
@@ -15608,26 +15948,26 @@
       </c>
       <c r="P118" s="12"/>
       <c r="Q118" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R118" s="14"/>
       <c r="S118" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T118" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U118" s="4"/>
       <c r="V118" s="20"/>
       <c r="W118" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X118" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y118" s="12">
@@ -15664,14 +16004,17 @@
         <v>1001017557514</v>
       </c>
       <c r="AJ118" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK118" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL118" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL118" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM118" s="16"/>
       <c r="AN118" s="16"/>
       <c r="AO118" s="16"/>
@@ -15717,11 +16060,11 @@
         <v>49</v>
       </c>
       <c r="L119" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-11</v>
       </c>
       <c r="M119" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>38</v>
       </c>
       <c r="N119" s="16"/>
@@ -15730,7 +16073,7 @@
       </c>
       <c r="P119" s="16"/>
       <c r="Q119" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>7.6</v>
       </c>
       <c r="R119" s="4">
@@ -15742,7 +16085,7 @@
         <v>91</v>
       </c>
       <c r="T119" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>91</v>
       </c>
       <c r="U119" s="4"/>
@@ -15750,11 +16093,11 @@
         <v>50</v>
       </c>
       <c r="W119" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>21.578947368421055</v>
       </c>
       <c r="X119" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>9.6052631578947381</v>
       </c>
       <c r="Y119" s="16">
@@ -15791,14 +16134,17 @@
         <v>77</v>
       </c>
       <c r="AJ119" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>28.21</v>
       </c>
       <c r="AK119" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL119" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL119" s="16">
+        <f t="shared" si="28"/>
+        <v>2.3559999999999999</v>
+      </c>
       <c r="AM119" s="16"/>
       <c r="AN119" s="16"/>
       <c r="AO119" s="16"/>
@@ -15834,11 +16180,11 @@
       <c r="J120" s="12"/>
       <c r="K120" s="12"/>
       <c r="L120" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M120" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N120" s="12"/>
@@ -15847,26 +16193,26 @@
       </c>
       <c r="P120" s="12"/>
       <c r="Q120" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R120" s="14"/>
       <c r="S120" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T120" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U120" s="4"/>
       <c r="V120" s="20"/>
       <c r="W120" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X120" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y120" s="12">
@@ -15903,14 +16249,17 @@
         <v>1001017567518</v>
       </c>
       <c r="AJ120" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK120" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL120" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL120" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM120" s="16"/>
       <c r="AN120" s="16"/>
       <c r="AO120" s="16"/>
@@ -15958,11 +16307,11 @@
         <v>295</v>
       </c>
       <c r="L121" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-21</v>
       </c>
       <c r="M121" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>214</v>
       </c>
       <c r="N121" s="16">
@@ -15973,7 +16322,7 @@
       </c>
       <c r="P121" s="16"/>
       <c r="Q121" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>42.8</v>
       </c>
       <c r="R121" s="4">
@@ -15985,7 +16334,7 @@
         <v>386</v>
       </c>
       <c r="T121" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>193</v>
       </c>
       <c r="U121" s="4">
@@ -15996,11 +16345,11 @@
         <v>40</v>
       </c>
       <c r="W121" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>12.94392523364486</v>
       </c>
       <c r="X121" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3.9252336448598135</v>
       </c>
       <c r="Y121" s="16">
@@ -16035,14 +16384,17 @@
       </c>
       <c r="AI121" s="16"/>
       <c r="AJ121" s="16">
-        <f t="shared" si="25"/>
-        <v>77.2</v>
-      </c>
-      <c r="AK121" s="16">
         <f t="shared" si="26"/>
         <v>77.2</v>
       </c>
-      <c r="AL121" s="16"/>
+      <c r="AK121" s="16">
+        <f t="shared" si="27"/>
+        <v>77.2</v>
+      </c>
+      <c r="AL121" s="16">
+        <f t="shared" si="28"/>
+        <v>17.12</v>
+      </c>
       <c r="AM121" s="16"/>
       <c r="AN121" s="16"/>
       <c r="AO121" s="16"/>
@@ -16078,11 +16430,11 @@
       <c r="J122" s="12"/>
       <c r="K122" s="12"/>
       <c r="L122" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M122" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N122" s="12"/>
@@ -16091,26 +16443,26 @@
       </c>
       <c r="P122" s="12"/>
       <c r="Q122" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R122" s="14"/>
       <c r="S122" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T122" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U122" s="4"/>
       <c r="V122" s="20"/>
       <c r="W122" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X122" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y122" s="12">
@@ -16147,14 +16499,17 @@
         <v>1001010017536</v>
       </c>
       <c r="AJ122" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK122" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL122" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL122" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM122" s="16"/>
       <c r="AN122" s="16"/>
       <c r="AO122" s="16"/>
@@ -16202,11 +16557,11 @@
         <v>242</v>
       </c>
       <c r="L123" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-112</v>
       </c>
       <c r="M123" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>130</v>
       </c>
       <c r="N123" s="16"/>
@@ -16215,7 +16570,7 @@
       </c>
       <c r="P123" s="16"/>
       <c r="Q123" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>26</v>
       </c>
       <c r="R123" s="4">
@@ -16223,21 +16578,21 @@
         <v>180</v>
       </c>
       <c r="S123" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>180</v>
       </c>
       <c r="T123" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>180</v>
       </c>
       <c r="U123" s="4"/>
       <c r="V123" s="21"/>
       <c r="W123" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7</v>
       </c>
       <c r="X123" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="Y123" s="16">
@@ -16274,14 +16629,17 @@
         <v>182</v>
       </c>
       <c r="AJ123" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>62.999999999999993</v>
       </c>
       <c r="AK123" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL123" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL123" s="16">
+        <f t="shared" si="28"/>
+        <v>9.1</v>
+      </c>
       <c r="AM123" s="16"/>
       <c r="AN123" s="16"/>
       <c r="AO123" s="16"/>
@@ -16327,11 +16685,11 @@
         <v>190.446</v>
       </c>
       <c r="L124" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-62.085000000000008</v>
       </c>
       <c r="M124" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>128.36099999999999</v>
       </c>
       <c r="N124" s="16"/>
@@ -16340,7 +16698,7 @@
       </c>
       <c r="P124" s="16"/>
       <c r="Q124" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>25.672199999999997</v>
       </c>
       <c r="R124" s="4">
@@ -16348,21 +16706,21 @@
         <v>175.49759999999998</v>
       </c>
       <c r="S124" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>175</v>
       </c>
       <c r="T124" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>175</v>
       </c>
       <c r="U124" s="4"/>
       <c r="V124" s="21"/>
       <c r="W124" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.9806171656500036</v>
       </c>
       <c r="X124" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>1.1639049243929231</v>
       </c>
       <c r="Y124" s="16">
@@ -16399,14 +16757,17 @@
         <v>77</v>
       </c>
       <c r="AJ124" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>175</v>
       </c>
       <c r="AK124" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL124" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL124" s="16">
+        <f t="shared" si="28"/>
+        <v>25.672199999999997</v>
+      </c>
       <c r="AM124" s="16"/>
       <c r="AN124" s="16"/>
       <c r="AO124" s="16"/>
@@ -16452,11 +16813,11 @@
         <v>15.8</v>
       </c>
       <c r="L125" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.67800000000000082</v>
       </c>
       <c r="M125" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>15.122</v>
       </c>
       <c r="N125" s="16"/>
@@ -16465,7 +16826,7 @@
       </c>
       <c r="P125" s="16"/>
       <c r="Q125" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>3.0244</v>
       </c>
       <c r="R125" s="4">
@@ -16473,21 +16834,21 @@
         <v>11.366</v>
       </c>
       <c r="S125" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>11</v>
       </c>
       <c r="T125" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11</v>
       </c>
       <c r="U125" s="4"/>
       <c r="V125" s="21"/>
       <c r="W125" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14.878984261341092</v>
       </c>
       <c r="X125" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>11.241899219679937</v>
       </c>
       <c r="Y125" s="16">
@@ -16524,14 +16885,17 @@
         <v>185</v>
       </c>
       <c r="AJ125" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11</v>
       </c>
       <c r="AK125" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL125" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL125" s="16">
+        <f t="shared" si="28"/>
+        <v>3.0244</v>
+      </c>
       <c r="AM125" s="16"/>
       <c r="AN125" s="16"/>
       <c r="AO125" s="16"/>
@@ -16577,11 +16941,11 @@
         <v>96</v>
       </c>
       <c r="L126" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-52</v>
       </c>
       <c r="M126" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>44</v>
       </c>
       <c r="N126" s="8"/>
@@ -16590,26 +16954,26 @@
       </c>
       <c r="P126" s="8"/>
       <c r="Q126" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="R126" s="10"/>
       <c r="S126" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T126" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U126" s="4"/>
       <c r="V126" s="22"/>
       <c r="W126" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>24.545454545454543</v>
       </c>
       <c r="X126" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>24.545454545454543</v>
       </c>
       <c r="Y126" s="8">
@@ -16646,14 +17010,17 @@
         <v>187</v>
       </c>
       <c r="AJ126" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK126" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL126" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL126" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM126" s="16"/>
       <c r="AN126" s="16"/>
       <c r="AO126" s="16"/>
@@ -16701,11 +17068,11 @@
         <v>199</v>
       </c>
       <c r="L127" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-46</v>
       </c>
       <c r="M127" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>113</v>
       </c>
       <c r="N127" s="16">
@@ -16716,7 +17083,7 @@
       </c>
       <c r="P127" s="16"/>
       <c r="Q127" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>22.6</v>
       </c>
       <c r="R127" s="4">
@@ -16728,7 +17095,7 @@
         <v>212</v>
       </c>
       <c r="T127" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>106</v>
       </c>
       <c r="U127" s="4">
@@ -16739,11 +17106,11 @@
         <v>40</v>
       </c>
       <c r="W127" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>14.778761061946902</v>
       </c>
       <c r="X127" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>5.3982300884955752</v>
       </c>
       <c r="Y127" s="16">
@@ -16780,14 +17147,17 @@
         <v>189</v>
       </c>
       <c r="AJ127" s="16">
-        <f t="shared" si="25"/>
-        <v>34.980000000000004</v>
-      </c>
-      <c r="AK127" s="16">
         <f t="shared" si="26"/>
         <v>34.980000000000004</v>
       </c>
-      <c r="AL127" s="16"/>
+      <c r="AK127" s="16">
+        <f t="shared" si="27"/>
+        <v>34.980000000000004</v>
+      </c>
+      <c r="AL127" s="16">
+        <f t="shared" si="28"/>
+        <v>7.4580000000000011</v>
+      </c>
       <c r="AM127" s="16"/>
       <c r="AN127" s="16"/>
       <c r="AO127" s="16"/>
@@ -16835,11 +17205,11 @@
         <v>172</v>
       </c>
       <c r="L128" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-166</v>
       </c>
       <c r="M128" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6</v>
       </c>
       <c r="N128" s="16"/>
@@ -16848,26 +17218,26 @@
       </c>
       <c r="P128" s="16"/>
       <c r="Q128" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>1.2</v>
       </c>
       <c r="R128" s="4"/>
       <c r="S128" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T128" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U128" s="4"/>
       <c r="V128" s="21"/>
       <c r="W128" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>20.833333333333336</v>
       </c>
       <c r="X128" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>20.833333333333336</v>
       </c>
       <c r="Y128" s="16">
@@ -16904,14 +17274,17 @@
         <v>190</v>
       </c>
       <c r="AJ128" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK128" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL128" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL128" s="16">
+        <f t="shared" si="28"/>
+        <v>0.12</v>
+      </c>
       <c r="AM128" s="16"/>
       <c r="AN128" s="16"/>
       <c r="AO128" s="16"/>
@@ -16959,11 +17332,11 @@
         <v>81</v>
       </c>
       <c r="L129" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-10</v>
       </c>
       <c r="M129" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>41</v>
       </c>
       <c r="N129" s="16">
@@ -16974,7 +17347,7 @@
       </c>
       <c r="P129" s="16"/>
       <c r="Q129" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="R129" s="4">
@@ -16982,21 +17355,21 @@
         <v>65.199999999999989</v>
       </c>
       <c r="S129" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>65</v>
       </c>
       <c r="T129" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>65</v>
       </c>
       <c r="U129" s="4"/>
       <c r="V129" s="21"/>
       <c r="W129" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>10.975609756097562</v>
       </c>
       <c r="X129" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3.0487804878048781</v>
       </c>
       <c r="Y129" s="16">
@@ -17033,14 +17406,17 @@
         <v>206</v>
       </c>
       <c r="AJ129" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6.5</v>
       </c>
       <c r="AK129" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL129" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL129" s="16">
+        <f t="shared" si="28"/>
+        <v>0.82</v>
+      </c>
       <c r="AM129" s="16"/>
       <c r="AN129" s="16"/>
       <c r="AO129" s="16"/>
@@ -17089,11 +17465,11 @@
         <v>172</v>
       </c>
       <c r="L130" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-6</v>
       </c>
       <c r="M130" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>126</v>
       </c>
       <c r="N130" s="16">
@@ -17104,7 +17480,7 @@
       </c>
       <c r="P130" s="16"/>
       <c r="Q130" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>25.2</v>
       </c>
       <c r="R130" s="4">
@@ -17112,21 +17488,21 @@
         <v>76</v>
       </c>
       <c r="S130" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>76</v>
       </c>
       <c r="T130" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>76</v>
       </c>
       <c r="U130" s="4"/>
       <c r="V130" s="21"/>
       <c r="W130" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X130" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>11.984126984126984</v>
       </c>
       <c r="Y130" s="16">
@@ -17163,14 +17539,17 @@
         <v>191</v>
       </c>
       <c r="AJ130" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.6000000000000005</v>
       </c>
       <c r="AK130" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL130" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL130" s="16">
+        <f t="shared" si="28"/>
+        <v>2.52</v>
+      </c>
       <c r="AM130" s="16"/>
       <c r="AN130" s="16"/>
       <c r="AO130" s="16"/>
@@ -17218,11 +17597,11 @@
         <v>307</v>
       </c>
       <c r="L131" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-59</v>
       </c>
       <c r="M131" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>208</v>
       </c>
       <c r="N131" s="16">
@@ -17235,26 +17614,26 @@
         <v>238</v>
       </c>
       <c r="Q131" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>41.6</v>
       </c>
       <c r="R131" s="4"/>
       <c r="S131" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T131" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U131" s="4"/>
       <c r="V131" s="21"/>
       <c r="W131" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>18.91826923076923</v>
       </c>
       <c r="X131" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>18.91826923076923</v>
       </c>
       <c r="Y131" s="16">
@@ -17291,14 +17670,17 @@
         <v>192</v>
       </c>
       <c r="AJ131" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK131" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL131" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL131" s="16">
+        <f t="shared" si="28"/>
+        <v>4.16</v>
+      </c>
       <c r="AM131" s="16"/>
       <c r="AN131" s="16"/>
       <c r="AO131" s="16"/>
@@ -17340,11 +17722,11 @@
         <v>20</v>
       </c>
       <c r="L132" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M132" s="12">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="N132" s="12">
@@ -17355,26 +17737,26 @@
       </c>
       <c r="P132" s="12"/>
       <c r="Q132" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="R132" s="14"/>
       <c r="S132" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="T132" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U132" s="4"/>
       <c r="V132" s="20"/>
       <c r="W132" s="16" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X132" s="12" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y132" s="12">
@@ -17411,14 +17793,17 @@
         <v>1001066607626</v>
       </c>
       <c r="AJ132" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AK132" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL132" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL132" s="16">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
       <c r="AM132" s="16"/>
       <c r="AN132" s="16"/>
       <c r="AO132" s="16"/>
@@ -17466,11 +17851,11 @@
         <v>612</v>
       </c>
       <c r="L133" s="16">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-111</v>
       </c>
       <c r="M133" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>469</v>
       </c>
       <c r="N133" s="16">
@@ -17483,7 +17868,7 @@
         <v>355</v>
       </c>
       <c r="Q133" s="16">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>93.8</v>
       </c>
       <c r="R133" s="4">
@@ -17491,11 +17876,11 @@
         <v>661</v>
       </c>
       <c r="S133" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>661</v>
       </c>
       <c r="T133" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>330</v>
       </c>
       <c r="U133" s="4">
@@ -17504,11 +17889,11 @@
       </c>
       <c r="V133" s="21"/>
       <c r="W133" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15</v>
       </c>
       <c r="X133" s="16">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>7.9530916844349679</v>
       </c>
       <c r="Y133" s="16">
@@ -17545,14 +17930,17 @@
         <v>194</v>
       </c>
       <c r="AJ133" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>132</v>
       </c>
       <c r="AK133" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>132.4</v>
       </c>
-      <c r="AL133" s="16"/>
+      <c r="AL133" s="16">
+        <f t="shared" si="28"/>
+        <v>37.520000000000003</v>
+      </c>
       <c r="AM133" s="16"/>
       <c r="AN133" s="16"/>
       <c r="AO133" s="16"/>
@@ -17598,11 +17986,11 @@
         <v>79</v>
       </c>
       <c r="L134" s="16">
-        <f t="shared" ref="L134:L139" si="37">E134-K134</f>
+        <f t="shared" ref="L134:L139" si="39">E134-K134</f>
         <v>-20</v>
       </c>
       <c r="M134" s="16">
-        <f t="shared" ref="M134:M139" si="38">E134-N134</f>
+        <f t="shared" ref="M134:M139" si="40">E134-N134</f>
         <v>59</v>
       </c>
       <c r="N134" s="16"/>
@@ -17611,7 +17999,7 @@
       </c>
       <c r="P134" s="16"/>
       <c r="Q134" s="16">
-        <f t="shared" ref="Q134:Q139" si="39">M134/5</f>
+        <f t="shared" ref="Q134:Q139" si="41">M134/5</f>
         <v>11.8</v>
       </c>
       <c r="R134" s="4">
@@ -17619,11 +18007,11 @@
         <v>12</v>
       </c>
       <c r="S134" s="4">
-        <f t="shared" ref="S134:S135" si="40">ROUND(R134,0)+V134</f>
+        <f t="shared" ref="S134:S135" si="42">ROUND(R134,0)+V134</f>
         <v>62</v>
       </c>
       <c r="T134" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>62</v>
       </c>
       <c r="U134" s="4"/>
@@ -17631,11 +18019,11 @@
         <v>50</v>
       </c>
       <c r="W134" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>19.237288135593218</v>
       </c>
       <c r="X134" s="16">
-        <f t="shared" ref="X134:X139" si="41">(F134+O134+P134)/Q134</f>
+        <f t="shared" ref="X134:X139" si="43">(F134+O134+P134)/Q134</f>
         <v>13.983050847457626</v>
       </c>
       <c r="Y134" s="16">
@@ -17672,14 +18060,17 @@
         <v>77</v>
       </c>
       <c r="AJ134" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6.2</v>
       </c>
       <c r="AK134" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AL134" s="16"/>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AL134" s="16">
+        <f t="shared" si="28"/>
+        <v>1.1800000000000002</v>
+      </c>
       <c r="AM134" s="16"/>
       <c r="AN134" s="16"/>
       <c r="AO134" s="16"/>
@@ -17725,11 +18116,11 @@
         <v>78</v>
       </c>
       <c r="L135" s="16">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-21</v>
       </c>
       <c r="M135" s="16">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>57</v>
       </c>
       <c r="N135" s="16"/>
@@ -17738,16 +18129,16 @@
       </c>
       <c r="P135" s="16"/>
       <c r="Q135" s="16">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>11.4</v>
       </c>
       <c r="R135" s="4"/>
       <c r="S135" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>50</v>
       </c>
       <c r="T135" s="4">
-        <f t="shared" ref="T135:T139" si="42">ROUND(S135-U135,0)</f>
+        <f t="shared" ref="T135:T139" si="44">ROUND(S135-U135,0)</f>
         <v>50</v>
       </c>
       <c r="U135" s="4"/>
@@ -17755,11 +18146,11 @@
         <v>50</v>
       </c>
       <c r="W135" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>19.649122807017545</v>
       </c>
       <c r="X135" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>15.263157894736842</v>
       </c>
       <c r="Y135" s="16">
@@ -17796,14 +18187,17 @@
         <v>77</v>
       </c>
       <c r="AJ135" s="16">
-        <f t="shared" ref="AJ135:AK139" si="43">G135*T135</f>
+        <f t="shared" ref="AJ135:AJ139" si="45">G135*T135</f>
         <v>5</v>
       </c>
       <c r="AK135" s="16">
-        <f t="shared" ref="AK135:AK139" si="44">G135*U135</f>
-        <v>0</v>
-      </c>
-      <c r="AL135" s="16"/>
+        <f t="shared" ref="AK135:AK139" si="46">G135*U135</f>
+        <v>0</v>
+      </c>
+      <c r="AL135" s="16">
+        <f t="shared" ref="AL135:AL139" si="47">Q135*G135</f>
+        <v>1.1400000000000001</v>
+      </c>
       <c r="AM135" s="16"/>
       <c r="AN135" s="16"/>
       <c r="AO135" s="16"/>
@@ -17839,11 +18233,11 @@
       <c r="J136" s="8"/>
       <c r="K136" s="8"/>
       <c r="L136" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M136" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N136" s="8"/>
@@ -17852,26 +18246,26 @@
       </c>
       <c r="P136" s="8"/>
       <c r="Q136" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R136" s="10"/>
       <c r="S136" s="4">
-        <f t="shared" ref="S136:S139" si="45">ROUND(R136,0)</f>
+        <f t="shared" ref="S136:S139" si="48">ROUND(R136,0)</f>
         <v>0</v>
       </c>
       <c r="T136" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U136" s="4"/>
       <c r="V136" s="22"/>
       <c r="W136" s="16" t="e">
-        <f t="shared" ref="W136:W139" si="46">(F136+O136+P136+S136)/Q136</f>
+        <f t="shared" ref="W136:W139" si="49">(F136+O136+P136+S136)/Q136</f>
         <v>#DIV/0!</v>
       </c>
       <c r="X136" s="8" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y136" s="8">
@@ -17908,14 +18302,17 @@
         <v>198</v>
       </c>
       <c r="AJ136" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AK136" s="16">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AL136" s="16"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AL136" s="16">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="AM136" s="16"/>
       <c r="AN136" s="16"/>
       <c r="AO136" s="16"/>
@@ -17959,11 +18356,11 @@
         <v>73.826999999999998</v>
       </c>
       <c r="L137" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M137" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N137" s="17">
@@ -17974,26 +18371,26 @@
       </c>
       <c r="P137" s="8"/>
       <c r="Q137" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R137" s="10"/>
       <c r="S137" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="T137" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U137" s="4"/>
       <c r="V137" s="22"/>
       <c r="W137" s="16" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X137" s="8" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y137" s="8">
@@ -18028,14 +18425,17 @@
       </c>
       <c r="AI137" s="8"/>
       <c r="AJ137" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AK137" s="16">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AL137" s="16"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AL137" s="16">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="AM137" s="16"/>
       <c r="AN137" s="16"/>
       <c r="AO137" s="16"/>
@@ -18079,11 +18479,11 @@
         <v>2</v>
       </c>
       <c r="L138" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-2</v>
       </c>
       <c r="M138" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N138" s="8"/>
@@ -18092,26 +18492,26 @@
       </c>
       <c r="P138" s="8"/>
       <c r="Q138" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R138" s="10"/>
       <c r="S138" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="T138" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U138" s="4"/>
       <c r="V138" s="22"/>
       <c r="W138" s="16" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X138" s="8" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y138" s="8">
@@ -18146,14 +18546,17 @@
       </c>
       <c r="AI138" s="8"/>
       <c r="AJ138" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AK138" s="16">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AL138" s="16"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AL138" s="16">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="AM138" s="16"/>
       <c r="AN138" s="16"/>
       <c r="AO138" s="16"/>
@@ -18199,11 +18602,11 @@
         <v>129.63</v>
       </c>
       <c r="L139" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M139" s="8">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N139" s="17">
@@ -18214,26 +18617,26 @@
       </c>
       <c r="P139" s="8"/>
       <c r="Q139" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R139" s="10"/>
       <c r="S139" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="T139" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="U139" s="4"/>
       <c r="V139" s="22"/>
       <c r="W139" s="16" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X139" s="8" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y139" s="8">
@@ -18268,14 +18671,17 @@
       </c>
       <c r="AI139" s="8"/>
       <c r="AJ139" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AK139" s="16">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="AL139" s="16"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AL139" s="16">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="AM139" s="16"/>
       <c r="AN139" s="16"/>
       <c r="AO139" s="16"/>
